--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158AE295-BBD4-45D8-879B-47F4A797DA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28809FAE-5B13-488E-B35A-11302330ECE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="472">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -77,10 +77,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>スタミナ</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>紅蓮の機王</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -353,10 +349,6 @@
   </si>
   <si>
     <t>ニジピィ(×4～5(※)),潜在たまドラ☆スキル遅延耐性(×3)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>バトル</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -1088,126 +1080,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>超重力</t>
-    <rPh sb="0" eb="3">
-      <t>チョウジュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>超高度</t>
-    <rPh sb="0" eb="3">
-      <t>チョウコウド</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>その他の効果</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陽/陰</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>イン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陰</t>
-    <rPh sb="0" eb="1">
-      <t>イン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陽</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/3333</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【灼熱】,HP10%減少,回復力1/2</t>
-    <rPh sb="1" eb="3">
-      <t>シャクネツ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ゲンショウ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>カイフクリョク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/3500</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【深緑】,木属性の攻撃力と回復力が2倍,お邪魔ドロップ目覚め(解除不可)</t>
-    <rPh sb="1" eb="3">
-      <t>フカミドリ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゾクセイ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>コウゲキリョク</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>カイフクリョク</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>バイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジャマ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>メザ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>カイジョフカ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/500</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/16</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/18</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/600</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/20</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>守霊の天体</t>
     <rPh sb="0" eb="1">
       <t>マモ</t>
@@ -1268,10 +1140,6 @@
     <rPh sb="3" eb="6">
       <t>シュゴシャ</t>
     </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陰</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -1427,22 +1295,6 @@
     <rPh sb="56" eb="57">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/2500</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/2</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/2000</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/4</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -2648,20 +2500,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>陽</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陰</t>
-    <rPh sb="0" eb="1">
-      <t>イン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>煉燼の百式龍・ビャクレンコウ：50周</t>
     <rPh sb="4" eb="5">
       <t>シキ</t>
@@ -2788,94 +2626,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/625</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/1000</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【回復タイプ強化】,回復タイプのHP1.5倍</t>
-    <rPh sb="1" eb="3">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/2</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【神タイプ強化】,神タイプのHP1.5倍</t>
-    <rPh sb="1" eb="2">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>約1/1428</t>
-    <rPh sb="0" eb="1">
-      <t>ヤク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/4</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【体力タイプ強化】,体力タイプのHP1.5倍</t>
-    <rPh sb="1" eb="3">
-      <t>タイリョク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タイリョク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>約1/1666</t>
-    <rPh sb="0" eb="1">
-      <t>ヤク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【バランスタイプ強化】,バランスタイプのHP1.5倍</t>
-    <rPh sb="8" eb="10">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>6,000万</t>
     <rPh sb="5" eb="6">
       <t>マン</t>
@@ -3671,17 +3421,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/50</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>陰</t>
-    <rPh sb="0" eb="1">
-      <t>イン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>蒼穹の千龍</t>
     <rPh sb="0" eb="2">
       <t>ソウキュウ</t>
@@ -3692,10 +3431,6 @@
     <rPh sb="4" eb="5">
       <t>リュウ</t>
     </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/80</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -3726,13 +3461,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>陽</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>5,000万</t>
     <rPh sb="5" eb="6">
       <t>マン</t>
@@ -3763,10 +3491,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/200</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>5,500万</t>
     <rPh sb="5" eb="6">
       <t>マン</t>
@@ -3794,14 +3518,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/100</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/4</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>6,000万</t>
     <rPh sb="5" eb="6">
       <t>マン</t>
@@ -3847,10 +3563,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/500</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>裏蒼穹の千龍</t>
     <rPh sb="0" eb="1">
       <t>ウラ</t>
@@ -3858,10 +3570,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/250</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>5,800万</t>
     <rPh sb="5" eb="6">
       <t>マン</t>
@@ -3885,10 +3593,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/400</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>35億</t>
     <rPh sb="2" eb="3">
       <t>オク</t>
@@ -3966,10 +3670,6 @@
     <rPh sb="1" eb="6">
       <t>ゴクアクセイメイタイ</t>
     </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/1000</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -4839,35 +4539,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/2000</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
-  </si>
-  <si>
-    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
-    <rPh sb="9" eb="11">
-      <t>ムコウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジョウセツ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>1億(ゲリラ時：10億)</t>
     <rPh sb="1" eb="2">
       <t>オク</t>
@@ -4926,10 +4597,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>【リーダーチェンジ無効】,※ゲリラ時のみで常設時は効果を受けない。</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>1.2億(ゲリラ時：12億)</t>
     <rPh sb="3" eb="4">
       <t>オク</t>
@@ -5130,10 +4797,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>1/2</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>1.3億(ゲリラ時：13億)</t>
     <rPh sb="3" eb="4">
       <t>オク</t>
@@ -5179,10 +4842,6 @@
     <rPh sb="24" eb="25">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>1/5000</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -6150,7 +5809,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6277,11 +5936,8 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6315,9 +5971,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6330,16 +5983,10 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -6361,7 +6008,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -6394,7 +6041,6 @@
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="桁区切り" xfId="42" builtinId="6"/>
     <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
@@ -6736,24 +6382,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
-    <col min="3" max="5" width="10.58203125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="156.4140625" style="17" customWidth="1"/>
-    <col min="7" max="8" width="30.58203125" style="18" customWidth="1"/>
-    <col min="9" max="9" width="75.58203125" style="17" customWidth="1"/>
-    <col min="10" max="14" width="25.58203125" style="17" customWidth="1"/>
-    <col min="15" max="15" width="163.75" style="16" customWidth="1"/>
-    <col min="16" max="16" width="71.1640625" style="16" customWidth="1"/>
-    <col min="17" max="17" width="71.08203125" style="16" customWidth="1"/>
-    <col min="18" max="18" width="255.5" style="16" customWidth="1"/>
-    <col min="19" max="19" width="151.1640625" style="16" customWidth="1"/>
-    <col min="20" max="20" width="104.1640625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="156.4140625" style="15" customWidth="1"/>
+    <col min="4" max="8" width="25.58203125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="163.75" style="14" customWidth="1"/>
+    <col min="10" max="10" width="71.1640625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="71.08203125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="255.5" style="14" customWidth="1"/>
+    <col min="13" max="13" width="151.1640625" style="14" customWidth="1"/>
+    <col min="14" max="14" width="104.1640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6761,1810 +6404,1276 @@
         <v>7</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="N1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9">
-        <v>99</v>
-      </c>
-      <c r="D2" s="9">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>99</v>
+        <v>33</v>
+      </c>
+      <c r="F2" s="10">
+        <v>2970</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="H2" s="10"/>
-      <c r="I2" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-    </row>
-    <row r="3" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J2" s="12"/>
+      <c r="K2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9">
-        <v>99</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="C3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-    </row>
-    <row r="4" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="9">
-        <v>99</v>
-      </c>
-      <c r="D4" s="9">
-        <v>12</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-    </row>
-    <row r="5" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J4" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9">
-        <v>99</v>
-      </c>
-      <c r="D5" s="9">
-        <v>15</v>
+      <c r="C5" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>102</v>
+        <v>34</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6666</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="11">
-        <v>6666</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="L5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="M5" s="12"/>
+      <c r="N5" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9">
-        <v>99</v>
-      </c>
-      <c r="D6" s="9">
-        <v>15</v>
+      <c r="C6" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="10">
+        <v>30</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="10" t="s">
+      <c r="D8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="11">
+      <c r="F9" s="10">
+        <v>7777</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="10">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="10">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" s="10">
         <v>2970</v>
       </c>
-      <c r="M6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="11">
+      <c r="G12" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="10">
+        <v>6600</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F16" s="10">
+        <v>5555</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="M16" s="12"/>
+      <c r="N16" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="10">
+        <v>7777</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F18" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="L19" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F21" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="K21" s="12"/>
+      <c r="L21" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F22" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F23" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F24" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="K25" s="12"/>
+      <c r="L25" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F26" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="K26" s="12"/>
+      <c r="L26" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F27" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="K27" s="12"/>
+      <c r="L27" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F28" s="10">
+        <v>2970</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" s="10">
+        <v>7777</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="J30" s="12"/>
+      <c r="K30" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="L30" s="12"/>
+      <c r="M30" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="L32" s="12"/>
+      <c r="M32" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9">
         <v>30</v>
       </c>
-      <c r="O6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="9">
-        <v>99</v>
-      </c>
-      <c r="D7" s="9">
-        <v>12</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="L7" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="T7" s="13"/>
-    </row>
-    <row r="8" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="9">
-        <v>99</v>
-      </c>
-      <c r="D8" s="9">
-        <v>13</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="L8" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="S8" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="T8" s="13"/>
-    </row>
-    <row r="9" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="9">
-        <v>99</v>
-      </c>
-      <c r="D9" s="9">
-        <v>13</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="L9" s="11">
-        <v>7777</v>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-    </row>
-    <row r="10" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="9">
-        <v>99</v>
-      </c>
-      <c r="D10" s="9">
-        <v>14</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="L10" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="S10" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="T10" s="13"/>
-    </row>
-    <row r="11" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="9">
-        <v>99</v>
-      </c>
-      <c r="D11" s="9">
-        <v>15</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="L11" s="11">
-        <v>9999</v>
-      </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q11" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="R11" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="S11" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="T11" s="12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="C12" s="9">
-        <v>99</v>
-      </c>
-      <c r="D12" s="9">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="L12" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-    </row>
-    <row r="13" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C13" s="9">
-        <v>99</v>
-      </c>
-      <c r="D13" s="9">
-        <v>10</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="L13" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-    </row>
-    <row r="14" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="9">
-        <v>99</v>
-      </c>
-      <c r="D14" s="9">
-        <v>11</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-    </row>
-    <row r="15" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C15" s="9">
-        <v>99</v>
-      </c>
-      <c r="D15" s="9">
-        <v>12</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L15" s="11">
-        <v>6600</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-    </row>
-    <row r="16" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C16" s="9">
-        <v>99</v>
-      </c>
-      <c r="D16" s="9">
-        <v>12</v>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="L16" s="11">
-        <v>5555</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="R16" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="S16" s="13"/>
-      <c r="T16" s="12" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C17" s="9">
-        <v>99</v>
-      </c>
-      <c r="D17" s="9">
-        <v>13</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="L17" s="11">
-        <v>7777</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="P17" s="12" t="s">
+      <c r="I33" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="J33" s="12"/>
+      <c r="K33" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="T17" s="24" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C18" s="9">
-        <v>99</v>
-      </c>
-      <c r="D18" s="9">
-        <v>16</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L18" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-    </row>
-    <row r="19" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="C19" s="9">
-        <v>99</v>
-      </c>
-      <c r="D19" s="9">
-        <v>16</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-    </row>
-    <row r="20" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C20" s="9">
-        <v>99</v>
-      </c>
-      <c r="D20" s="9">
-        <v>15</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-    </row>
-    <row r="21" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C21" s="9">
-        <v>99</v>
-      </c>
-      <c r="D21" s="9">
-        <v>16</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="L21" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-    </row>
-    <row r="22" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C22" s="9">
-        <v>99</v>
-      </c>
-      <c r="D22" s="9">
-        <v>16</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="L22" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="12" t="s">
+      <c r="E34" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="J34" s="12"/>
+      <c r="K34" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="11" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="12" t="s">
+      <c r="D35" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-    </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C23" s="9">
-        <v>99</v>
-      </c>
-      <c r="D23" s="9">
-        <v>15</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="L23" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="T23" s="13"/>
-    </row>
-    <row r="24" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C24" s="9">
-        <v>99</v>
-      </c>
-      <c r="D24" s="9">
-        <v>16</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="L24" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-    </row>
-    <row r="25" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C25" s="9">
-        <v>99</v>
-      </c>
-      <c r="D25" s="9">
-        <v>16</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="L25" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="P25" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-    </row>
-    <row r="26" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="C26" s="9">
-        <v>99</v>
-      </c>
-      <c r="D26" s="9">
-        <v>15</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="L26" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-    </row>
-    <row r="27" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="9">
-        <v>99</v>
-      </c>
-      <c r="D27" s="9">
-        <v>16</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="L27" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-    </row>
-    <row r="28" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C28" s="9">
-        <v>99</v>
-      </c>
-      <c r="D28" s="9">
-        <v>16</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="L28" s="11">
-        <v>2970</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-    </row>
-    <row r="29" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="9">
-        <v>99</v>
-      </c>
-      <c r="D29" s="9">
-        <v>15</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="L29" s="11">
-        <v>7777</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="N29" s="9"/>
-      <c r="O29" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="S29" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="T29" s="13"/>
-    </row>
-    <row r="30" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="E35" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9">
+        <v>30</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="J36" s="12"/>
+      <c r="K36" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="L36" s="12"/>
+      <c r="M36" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="N36" s="11" t="s">
         <v>441</v>
-      </c>
-      <c r="C30" s="9">
-        <v>99</v>
-      </c>
-      <c r="D30" s="9">
-        <v>15</v>
-      </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="R30" s="13"/>
-      <c r="S30" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="T30" s="12" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="C31" s="9">
-        <v>99</v>
-      </c>
-      <c r="D31" s="9">
-        <v>15</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q31" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="R31" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="S31" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="T31" s="13"/>
-    </row>
-    <row r="32" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="C32" s="9">
-        <v>99</v>
-      </c>
-      <c r="D32" s="9">
-        <v>15</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H32" s="10"/>
-      <c r="I32" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="R32" s="13"/>
-      <c r="S32" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="T32" s="12" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="C33" s="9">
-        <v>99</v>
-      </c>
-      <c r="D33" s="9">
-        <v>16</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H33" s="10"/>
-      <c r="I33" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9">
-        <v>30</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="R33" s="13"/>
-      <c r="S33" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="T33" s="12" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C34" s="9">
-        <v>99</v>
-      </c>
-      <c r="D34" s="9">
-        <v>15</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="R34" s="13"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C35" s="9">
-        <v>99</v>
-      </c>
-      <c r="D35" s="9">
-        <v>15</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="S35" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="T35" s="12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>447</v>
-      </c>
-      <c r="C36" s="9">
-        <v>99</v>
-      </c>
-      <c r="D36" s="9">
-        <v>15</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9">
-        <v>30</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>507</v>
-      </c>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="R36" s="13"/>
-      <c r="S36" s="12" t="s">
-        <v>509</v>
-      </c>
-      <c r="T36" s="12" t="s">
-        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -8585,10 +7694,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8596,7 +7705,7 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8604,7 +7713,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8612,7 +7721,7 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8620,7 +7729,7 @@
         <v>1077</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8628,7 +7737,7 @@
         <v>1081</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8636,7 +7745,7 @@
         <v>1083</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8644,7 +7753,7 @@
         <v>1341</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8652,7 +7761,7 @@
         <v>1547</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8660,7 +7769,7 @@
         <v>1548</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8668,7 +7777,7 @@
         <v>1549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8676,7 +7785,7 @@
         <v>1550</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8684,7 +7793,7 @@
         <v>1551</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8692,7 +7801,7 @@
         <v>1709</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8700,7 +7809,7 @@
         <v>2250</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8708,7 +7817,7 @@
         <v>2425</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8716,7 +7825,7 @@
         <v>3317</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8724,7 +7833,7 @@
         <v>3318</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8732,7 +7841,7 @@
         <v>3319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8740,7 +7849,7 @@
         <v>3320</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8748,7 +7857,7 @@
         <v>3321</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8756,7 +7865,7 @@
         <v>3322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8764,7 +7873,7 @@
         <v>3323</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8772,7 +7881,7 @@
         <v>3324</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8780,7 +7889,7 @@
         <v>3325</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8788,7 +7897,7 @@
         <v>3700</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8796,7 +7905,7 @@
         <v>3701</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8804,7 +7913,7 @@
         <v>3702</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8812,7 +7921,7 @@
         <v>3795</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8820,7 +7929,7 @@
         <v>3827</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8828,7 +7937,7 @@
         <v>3891</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8836,7 +7945,7 @@
         <v>3911</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8844,7 +7953,7 @@
         <v>3971</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8852,7 +7961,7 @@
         <v>3973</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8860,7 +7969,7 @@
         <v>3974</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8868,7 +7977,7 @@
         <v>4014</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8876,7 +7985,7 @@
         <v>4369</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8884,7 +7993,7 @@
         <v>4370</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8892,7 +8001,7 @@
         <v>4371</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8900,7 +8009,7 @@
         <v>4372</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8908,7 +8017,7 @@
         <v>4373</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8916,7 +8025,7 @@
         <v>5739</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8924,7 +8033,7 @@
         <v>6073</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8932,7 +8041,7 @@
         <v>6074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8940,7 +8049,7 @@
         <v>6075</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8948,7 +8057,7 @@
         <v>6076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8956,7 +8065,7 @@
         <v>6077</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8964,7 +8073,7 @@
         <v>6178</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8972,7 +8081,7 @@
         <v>6522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8980,7 +8089,7 @@
         <v>6607</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8988,7 +8097,7 @@
         <v>6608</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -8996,7 +8105,7 @@
         <v>6609</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9004,7 +8113,7 @@
         <v>6878</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9012,7 +8121,7 @@
         <v>7020</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9020,7 +8129,7 @@
         <v>7021</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9028,7 +8137,7 @@
         <v>7022</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9036,7 +8145,7 @@
         <v>7023</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9044,7 +8153,7 @@
         <v>7042</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9052,7 +8161,7 @@
         <v>7493</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9060,7 +8169,7 @@
         <v>8298</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9068,7 +8177,7 @@
         <v>8551</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9076,7 +8185,7 @@
         <v>8552</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>312</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9084,7 +8193,7 @@
         <v>8553</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9092,7 +8201,7 @@
         <v>8554</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9100,7 +8209,7 @@
         <v>8555</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9108,7 +8217,7 @@
         <v>8728</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9116,7 +8225,7 @@
         <v>9000</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9124,7 +8233,7 @@
         <v>9454</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9132,7 +8241,7 @@
         <v>9534</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9140,7 +8249,7 @@
         <v>10022</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9148,7 +8257,7 @@
         <v>10023</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9156,7 +8265,7 @@
         <v>10024</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9164,7 +8273,7 @@
         <v>10025</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9172,7 +8281,7 @@
         <v>10026</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9180,7 +8289,7 @@
         <v>10114</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9188,7 +8297,7 @@
         <v>10512</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9196,7 +8305,7 @@
         <v>10513</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9204,7 +8313,7 @@
         <v>10514</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9212,7 +8321,7 @@
         <v>10515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9220,7 +8329,7 @@
         <v>10516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9228,7 +8337,7 @@
         <v>10517</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9236,7 +8345,7 @@
         <v>10518</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9244,7 +8353,7 @@
         <v>10519</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9252,7 +8361,7 @@
         <v>10520</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9260,7 +8369,7 @@
         <v>10521</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9268,7 +8377,7 @@
         <v>10528</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9276,7 +8385,7 @@
         <v>10529</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9284,7 +8393,7 @@
         <v>10530</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9292,7 +8401,7 @@
         <v>10533</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9300,7 +8409,7 @@
         <v>11108</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9308,7 +8417,7 @@
         <v>11119</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9316,7 +8425,7 @@
         <v>11196</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9324,7 +8433,7 @@
         <v>11207</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9332,7 +8441,7 @@
         <v>11552</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9340,7 +8449,7 @@
         <v>11556</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9348,7 +8457,7 @@
         <v>11559</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9356,7 +8465,7 @@
         <v>11562</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9364,7 +8473,7 @@
         <v>11565</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9372,7 +8481,7 @@
         <v>11568</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9380,7 +8489,7 @@
         <v>11588</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9388,7 +8497,7 @@
         <v>12257</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9396,7 +8505,7 @@
         <v>12258</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9404,7 +8513,7 @@
         <v>12261</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9412,7 +8521,7 @@
         <v>12691</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9420,7 +8529,7 @@
         <v>12692</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9428,7 +8537,7 @@
         <v>12693</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9436,7 +8545,7 @@
         <v>12696</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9444,7 +8553,7 @@
         <v>12697</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9452,7 +8561,7 @@
         <v>12863</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9460,7 +8569,7 @@
         <v>12864</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9468,7 +8577,7 @@
         <v>12865</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9476,7 +8585,7 @@
         <v>12866</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9484,7 +8593,7 @@
         <v>12869</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9492,7 +8601,7 @@
         <v>13055</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9500,7 +8609,7 @@
         <v>13056</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9508,7 +8617,7 @@
         <v>13057</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9516,7 +8625,7 @@
         <v>13060</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9524,7 +8633,7 @@
         <v>13295</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9532,7 +8641,7 @@
         <v>13381</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9540,7 +8649,7 @@
         <v>13382</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9548,7 +8657,7 @@
         <v>13383</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9556,7 +8665,7 @@
         <v>13384</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9564,7 +8673,7 @@
         <v>13499</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9572,7 +8681,7 @@
         <v>13500</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9580,7 +8689,7 @@
         <v>13501</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9588,7 +8697,7 @@
         <v>13503</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9596,7 +8705,7 @@
         <v>13590</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9604,7 +8713,7 @@
         <v>13591</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9612,7 +8721,7 @@
         <v>13592</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9620,7 +8729,7 @@
         <v>13594</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9628,7 +8737,7 @@
         <v>13667</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9636,7 +8745,7 @@
         <v>13799</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9644,7 +8753,7 @@
         <v>13800</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9652,7 +8761,7 @@
         <v>13801</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9660,7 +8769,7 @@
         <v>13803</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9668,7 +8777,7 @@
         <v>13821</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9676,7 +8785,7 @@
         <v>13822</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9684,7 +8793,7 @@
         <v>13823</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9692,7 +8801,7 @@
         <v>13825</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9700,7 +8809,7 @@
         <v>14023</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9708,7 +8817,7 @@
         <v>14024</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9716,7 +8825,7 @@
         <v>14025</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9724,7 +8833,7 @@
         <v>14027</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9732,7 +8841,7 @@
         <v>8914</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9740,7 +8849,7 @@
         <v>8916</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9748,7 +8857,7 @@
         <v>7680</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9756,7 +8865,7 @@
         <v>7681</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9764,7 +8873,7 @@
         <v>7684</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9772,7 +8881,7 @@
         <v>7686</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9780,7 +8889,7 @@
         <v>9227</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9788,7 +8897,7 @@
         <v>9229</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9796,7 +8905,7 @@
         <v>9455</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9804,7 +8913,7 @@
         <v>9457</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9812,7 +8921,7 @@
         <v>9716</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9820,7 +8929,7 @@
         <v>9827</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9828,7 +8937,7 @@
         <v>322</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9836,7 +8945,7 @@
         <v>323</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>393</v>
+        <v>348</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9844,7 +8953,7 @@
         <v>324</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9852,7 +8961,7 @@
         <v>325</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9860,7 +8969,7 @@
         <v>1109</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9868,7 +8977,7 @@
         <v>326</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9876,7 +8985,7 @@
         <v>327</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9884,7 +8993,7 @@
         <v>328</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9892,7 +9001,7 @@
         <v>329</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9900,7 +9009,7 @@
         <v>1095</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9908,7 +9017,7 @@
         <v>330</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9916,7 +9025,7 @@
         <v>331</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9924,7 +9033,7 @@
         <v>332</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9932,7 +9041,7 @@
         <v>333</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9940,7 +9049,7 @@
         <v>1096</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9948,7 +9057,7 @@
         <v>334</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9956,7 +9065,7 @@
         <v>335</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9964,7 +9073,7 @@
         <v>336</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9972,7 +9081,7 @@
         <v>337</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9980,7 +9089,7 @@
         <v>1110</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9988,7 +9097,7 @@
         <v>338</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9996,7 +9105,7 @@
         <v>339</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>413</v>
+        <v>368</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10004,7 +9113,7 @@
         <v>340</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10012,7 +9121,7 @@
         <v>341</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10020,7 +9129,7 @@
         <v>1111</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10028,7 +9137,7 @@
         <v>11046</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10036,7 +9145,7 @@
         <v>11039</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10044,7 +9153,7 @@
         <v>11040</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>421</v>
+        <v>376</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10052,7 +9161,7 @@
         <v>11037</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>422</v>
+        <v>377</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10060,7 +9169,7 @@
         <v>11038</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10068,7 +9177,7 @@
         <v>1340</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10076,7 +9185,7 @@
         <v>13047</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10084,7 +9193,7 @@
         <v>13048</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10092,7 +9201,7 @@
         <v>3826</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10100,7 +9209,7 @@
         <v>1325</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10108,7 +9217,7 @@
         <v>1326</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10116,7 +9225,7 @@
         <v>1327</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10124,7 +9233,7 @@
         <v>1328</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>504</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10132,7 +9241,7 @@
         <v>1329</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10140,7 +9249,7 @@
         <v>13303</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10148,7 +9257,7 @@
         <v>13304</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10156,7 +9265,7 @@
         <v>12345</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>512</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10164,7 +9273,7 @@
         <v>12346</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>513</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10172,7 +9281,7 @@
         <v>12114</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>514</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10180,7 +9289,7 @@
         <v>11217</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10188,7 +9297,7 @@
         <v>11218</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -10205,31 +9314,31 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.08203125" style="19" customWidth="1"/>
+    <col min="1" max="1" width="17.08203125" style="16" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="19" t="s">
-        <v>223</v>
+      <c r="A1" s="16" t="s">
+        <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="20">
+      <c r="A2" s="17">
         <v>46264</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -10243,29 +9352,29 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="15.58203125" style="23" customWidth="1"/>
+    <col min="2" max="3" width="15.58203125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="B1" t="s">
-        <v>518</v>
+        <v>467</v>
       </c>
       <c r="C1" t="s">
-        <v>519</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>520</v>
+      <c r="B2" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28809FAE-5B13-488E-B35A-11302330ECE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD0C21E-1507-4FE6-8295-C92259A0C98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="490">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5260,6 +5260,174 @@
   </si>
   <si>
     <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2)(※3))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級2人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級3人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級4人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級5人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級6人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級7人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>∞級8人専用コロシアム</t>
+    <rPh sb="0" eb="2">
+      <t>ムゲンキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>轟爆の鳳凰帝</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウバク</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ホウオウテイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>1.4億</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【スペード7】のトランプ兵</t>
+    <rPh sb="12" eb="13">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【ハート7】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【ダイヤ7】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【クラブ7】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【ハート5】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【ダイヤ4】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【スペード3】のトランプ兵</t>
+    <rPh sb="12" eb="13">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【クラブ2】のトランプ兵</t>
+    <rPh sb="11" eb="12">
+      <t>ヘイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【スペード7】のトランプ兵,【ハート7】のトランプ兵,【ダイヤ7】のトランプ兵,【クラブ7】のトランプ兵,【ハート5】のトランプ兵,【ダイヤ4】のトランプ兵,【スペード3】のトランプ兵,【クラブ2】のトランプ兵(×3),潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×5),潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×5)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -5937,7 +6105,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6006,6 +6174,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -6382,7 +6560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
@@ -6441,7 +6619,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -6477,7 +6655,7 @@
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -6515,7 +6693,7 @@
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -6551,7 +6729,7 @@
       <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -6591,7 +6769,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -6633,7 +6811,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -6671,7 +6849,7 @@
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -6709,7 +6887,7 @@
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -6745,7 +6923,7 @@
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -6783,7 +6961,7 @@
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -6823,7 +7001,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B12" s="18" t="s">
@@ -6859,7 +7037,7 @@
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -6893,7 +7071,7 @@
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -6929,7 +7107,7 @@
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -6965,7 +7143,7 @@
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -7005,7 +7183,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -7045,7 +7223,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -7077,7 +7255,7 @@
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -7107,7 +7285,7 @@
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -7137,7 +7315,7 @@
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -7169,7 +7347,7 @@
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -7201,7 +7379,7 @@
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -7235,7 +7413,7 @@
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -7265,7 +7443,7 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -7297,7 +7475,7 @@
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -7329,7 +7507,7 @@
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -7361,7 +7539,7 @@
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -7395,7 +7573,7 @@
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -7431,7 +7609,7 @@
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="22" t="s">
         <v>395</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -7467,8 +7645,8 @@
       </c>
     </row>
     <row r="31" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="6" t="s">
-        <v>395</v>
+      <c r="A31" s="22" t="s">
+        <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>397</v>
@@ -7505,8 +7683,8 @@
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="6" t="s">
-        <v>395</v>
+      <c r="A32" s="22" t="s">
+        <v>473</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>398</v>
@@ -7539,8 +7717,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="6" t="s">
-        <v>395</v>
+      <c r="A33" s="22" t="s">
+        <v>474</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>399</v>
@@ -7575,8 +7753,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="6" t="s">
-        <v>395</v>
+      <c r="A34" s="22" t="s">
+        <v>475</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>400</v>
@@ -7607,8 +7785,8 @@
       </c>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="6" t="s">
-        <v>395</v>
+      <c r="A35" s="22" t="s">
+        <v>476</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>401</v>
@@ -7641,8 +7819,8 @@
       </c>
     </row>
     <row r="36" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="6" t="s">
-        <v>395</v>
+      <c r="A36" s="22" t="s">
+        <v>477</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>402</v>
@@ -7673,9 +7851,72 @@
         <v>458</v>
       </c>
       <c r="N36" s="11" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="H37" s="15">
+        <v>30</v>
+      </c>
+      <c r="K37" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="N37" s="23" t="s">
         <v>441</v>
       </c>
     </row>
+    <row r="38" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="39" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="40" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="41" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="42" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="44" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="45" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="46" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="47" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="48" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="49" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="50" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="51" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="52" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="53" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="54" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="55" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="56" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="57" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="58" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="59" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="60" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="61" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="62" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="63" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="64" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="65" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="66" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="67" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="68" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="69" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="70" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="71" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="72" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="73" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="74" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7685,7 +7926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -7726,1583 +7967,1647 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3">
-        <v>1077</v>
+        <v>322</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
-        <v>1081</v>
+        <v>323</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
-        <v>1083</v>
+        <v>324</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
-        <v>1341</v>
+        <v>325</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>224</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
-        <v>1547</v>
+        <v>326</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>177</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
-        <v>1548</v>
+        <v>327</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>178</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
-        <v>1549</v>
+        <v>328</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
-        <v>1550</v>
+        <v>329</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>180</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
-        <v>1551</v>
+        <v>330</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>181</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
-        <v>1709</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
-        <v>2250</v>
+        <v>332</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>61</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
-        <v>2425</v>
+        <v>333</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
-        <v>3317</v>
+        <v>334</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>136</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
-        <v>3318</v>
+        <v>335</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>227</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
-        <v>3319</v>
+        <v>336</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>228</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
-        <v>3320</v>
+        <v>337</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>229</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
-        <v>3321</v>
+        <v>338</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>230</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
-        <v>3322</v>
+        <v>339</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
-        <v>3323</v>
+        <v>340</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>232</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
-        <v>3324</v>
+        <v>341</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>233</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
-        <v>3325</v>
+        <v>1077</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>234</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
-        <v>3700</v>
+        <v>1081</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
-        <v>3701</v>
+        <v>1083</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
-        <v>3702</v>
+        <v>1095</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
-        <v>3795</v>
+        <v>1096</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
-        <v>3827</v>
+        <v>1109</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>226</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
-        <v>3891</v>
+        <v>1110</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>60</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
-        <v>3911</v>
+        <v>1111</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>55</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
-        <v>3971</v>
+        <v>1325</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>56</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
-        <v>3973</v>
+        <v>1326</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>59</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
-        <v>3974</v>
+        <v>1327</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>137</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
-        <v>4014</v>
+        <v>1328</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>138</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
-        <v>4369</v>
+        <v>1329</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>48</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
-        <v>4370</v>
+        <v>1340</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
-        <v>4371</v>
+        <v>1341</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>50</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3">
-        <v>4372</v>
+        <v>1547</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3">
-        <v>4373</v>
+        <v>1548</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3">
-        <v>5739</v>
+        <v>1549</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3">
-        <v>6073</v>
+        <v>1550</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3">
-        <v>6074</v>
+        <v>1551</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3">
-        <v>6075</v>
+        <v>1709</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3">
-        <v>6076</v>
+        <v>2250</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3">
-        <v>6077</v>
+        <v>2425</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3">
-        <v>6178</v>
+        <v>3317</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3">
-        <v>6522</v>
+        <v>3318</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3">
-        <v>6607</v>
+        <v>3319</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>162</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3">
-        <v>6608</v>
+        <v>3320</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3">
-        <v>6609</v>
+        <v>3321</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>164</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3">
-        <v>6878</v>
+        <v>3322</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3">
-        <v>7020</v>
+        <v>3323</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3">
-        <v>7021</v>
+        <v>3324</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>45</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3">
-        <v>7022</v>
+        <v>3325</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3">
-        <v>7023</v>
+        <v>3700</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3">
-        <v>7042</v>
+        <v>3701</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3">
-        <v>7493</v>
+        <v>3702</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3">
-        <v>8298</v>
+        <v>3795</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3">
-        <v>8551</v>
+        <v>3826</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>277</v>
+        <v>446</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3">
-        <v>8552</v>
+        <v>3827</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3">
-        <v>8553</v>
+        <v>3891</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>279</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3">
-        <v>8554</v>
+        <v>3911</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>280</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
-        <v>8555</v>
+        <v>3971</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>281</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
-        <v>8728</v>
+        <v>3973</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
-        <v>9000</v>
+        <v>3974</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
-        <v>9454</v>
+        <v>4014</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
-        <v>9534</v>
+        <v>4369</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
-        <v>10022</v>
+        <v>4370</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
-        <v>10023</v>
+        <v>4371</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3">
-        <v>10024</v>
+        <v>4372</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3">
-        <v>10025</v>
+        <v>4373</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3">
-        <v>10026</v>
+        <v>5739</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3">
-        <v>10114</v>
+        <v>6073</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3">
-        <v>10512</v>
+        <v>6074</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3">
-        <v>10513</v>
+        <v>6075</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3">
-        <v>10514</v>
+        <v>6076</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3">
-        <v>10515</v>
+        <v>6077</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3">
-        <v>10516</v>
+        <v>6178</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3">
-        <v>10517</v>
+        <v>6522</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
-        <v>10518</v>
+        <v>6607</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
-        <v>10519</v>
+        <v>6608</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
-        <v>10520</v>
+        <v>6609</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
-        <v>10521</v>
+        <v>6878</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
-        <v>10528</v>
+        <v>7020</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
-        <v>10529</v>
+        <v>7021</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
-        <v>10530</v>
+        <v>7022</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
-        <v>10533</v>
+        <v>7023</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
-        <v>11108</v>
+        <v>7042</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
-        <v>11119</v>
+        <v>7493</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
-        <v>11196</v>
+        <v>7680</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>240</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
-        <v>11207</v>
+        <v>7681</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>244</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
-        <v>11552</v>
+        <v>7684</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
-        <v>11556</v>
+        <v>7686</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
-        <v>11559</v>
+        <v>8298</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
-        <v>11562</v>
+        <v>8551</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
-        <v>11565</v>
+        <v>8552</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
-        <v>11568</v>
+        <v>8553</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
-        <v>11588</v>
+        <v>8554</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
-        <v>12257</v>
+        <v>8555</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
-        <v>12258</v>
+        <v>8728</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>270</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
-        <v>12261</v>
+        <v>8914</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
-        <v>12691</v>
+        <v>8916</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>142</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
-        <v>12692</v>
+        <v>9000</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
-        <v>12693</v>
+        <v>9227</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3">
-        <v>12696</v>
+        <v>9229</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>145</v>
+        <v>333</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
-        <v>12697</v>
+        <v>9454</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
-        <v>12863</v>
+        <v>9455</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>153</v>
+        <v>337</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
-        <v>12864</v>
+        <v>9457</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>154</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
-        <v>12865</v>
+        <v>9534</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
-        <v>12866</v>
+        <v>9716</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3">
-        <v>12869</v>
+        <v>9827</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>157</v>
+        <v>343</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3">
-        <v>13055</v>
+        <v>10022</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3">
-        <v>13056</v>
+        <v>10023</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3">
-        <v>13057</v>
+        <v>10024</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3">
-        <v>13060</v>
+        <v>10025</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3">
-        <v>13295</v>
+        <v>10026</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>193</v>
+        <v>74</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3">
-        <v>13381</v>
+        <v>10114</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3">
-        <v>13382</v>
+        <v>10512</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3">
-        <v>13383</v>
+        <v>10513</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3">
-        <v>13384</v>
+        <v>10514</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3">
-        <v>13499</v>
+        <v>10515</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3">
-        <v>13500</v>
+        <v>10516</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3">
-        <v>13501</v>
+        <v>10517</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>86</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3">
-        <v>13503</v>
+        <v>10518</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3">
-        <v>13590</v>
+        <v>10519</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3">
-        <v>13591</v>
+        <v>10520</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3">
-        <v>13592</v>
+        <v>10521</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3">
-        <v>13594</v>
+        <v>10528</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3">
-        <v>13667</v>
+        <v>10529</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3">
-        <v>13799</v>
+        <v>10530</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3">
-        <v>13800</v>
+        <v>10533</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3">
-        <v>13801</v>
+        <v>11037</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>90</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3">
-        <v>13803</v>
+        <v>11038</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>91</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3">
-        <v>13821</v>
+        <v>11039</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>76</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3">
-        <v>13822</v>
+        <v>11040</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>77</v>
+        <v>376</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3">
-        <v>13823</v>
+        <v>11046</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="3">
-        <v>13825</v>
+        <v>11108</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="3">
-        <v>14023</v>
+        <v>11119</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3">
-        <v>14024</v>
+        <v>11196</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>93</v>
+        <v>240</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="3">
-        <v>14025</v>
+        <v>11207</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="3">
-        <v>14027</v>
+        <v>11217</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>95</v>
+        <v>464</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="3">
-        <v>8914</v>
+        <v>11218</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>323</v>
+        <v>465</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="3">
-        <v>8916</v>
+        <v>11552</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>324</v>
+        <v>245</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="3">
-        <v>7680</v>
+        <v>11556</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>327</v>
+        <v>257</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="3">
-        <v>7681</v>
+        <v>11559</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>328</v>
+        <v>258</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="3">
-        <v>7684</v>
+        <v>11562</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>329</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="3">
-        <v>7686</v>
+        <v>11565</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>330</v>
+        <v>260</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="3">
-        <v>9227</v>
+        <v>11568</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>332</v>
+        <v>261</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="3">
-        <v>9229</v>
+        <v>11588</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>333</v>
+        <v>246</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="3">
-        <v>9455</v>
+        <v>12114</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>337</v>
+        <v>463</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="3">
-        <v>9457</v>
+        <v>12257</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>338</v>
+        <v>268</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="3">
-        <v>9716</v>
+        <v>12258</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>342</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="3">
-        <v>9827</v>
+        <v>12261</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>343</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="3">
-        <v>322</v>
+        <v>12345</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="3">
-        <v>323</v>
+        <v>12346</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="3">
-        <v>324</v>
+        <v>12691</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>349</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="3">
-        <v>325</v>
+        <v>12692</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>350</v>
+        <v>143</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="3">
-        <v>1109</v>
+        <v>12693</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>351</v>
+        <v>144</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="3">
-        <v>326</v>
+        <v>12696</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>352</v>
+        <v>145</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="3">
-        <v>327</v>
+        <v>12697</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>353</v>
+        <v>146</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="3">
-        <v>328</v>
+        <v>12863</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>354</v>
+        <v>153</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="3">
-        <v>329</v>
+        <v>12864</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>355</v>
+        <v>154</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="3">
-        <v>1095</v>
+        <v>12865</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>356</v>
+        <v>155</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="3">
-        <v>330</v>
+        <v>12866</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>357</v>
+        <v>156</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="3">
-        <v>331</v>
+        <v>12869</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>358</v>
+        <v>157</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="3">
-        <v>332</v>
+        <v>13047</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>359</v>
+        <v>443</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="3">
-        <v>333</v>
+        <v>13048</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="3">
-        <v>1096</v>
+        <v>13055</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>361</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="3">
-        <v>334</v>
+        <v>13056</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>362</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="3">
-        <v>335</v>
+        <v>13057</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>363</v>
+        <v>175</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="3">
-        <v>336</v>
+        <v>13060</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>364</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="3">
-        <v>337</v>
+        <v>13295</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>365</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="3">
-        <v>1110</v>
+        <v>13303</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="3">
-        <v>338</v>
+        <v>13304</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="3">
-        <v>339</v>
+        <v>13381</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>368</v>
+        <v>189</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="3">
-        <v>340</v>
+        <v>13382</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>369</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="3">
-        <v>341</v>
+        <v>13383</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>371</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="3">
-        <v>1111</v>
+        <v>13384</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>370</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="3">
-        <v>11046</v>
+        <v>13499</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>374</v>
+        <v>84</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="3">
-        <v>11039</v>
+        <v>13500</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>375</v>
+        <v>85</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="3">
-        <v>11040</v>
+        <v>13501</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>376</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="3">
-        <v>11037</v>
+        <v>13503</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>377</v>
+        <v>87</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="3">
-        <v>11038</v>
+        <v>13590</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="3">
-        <v>1340</v>
+        <v>13591</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>387</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="3">
-        <v>13047</v>
+        <v>13592</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="3">
-        <v>13048</v>
+        <v>13594</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>444</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="3">
-        <v>3826</v>
+        <v>13667</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>446</v>
+        <v>64</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="3">
-        <v>1325</v>
+        <v>13799</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>450</v>
+        <v>88</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="3">
-        <v>1326</v>
+        <v>13800</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>451</v>
+        <v>89</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="3">
-        <v>1327</v>
+        <v>13801</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>452</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="3">
-        <v>1328</v>
+        <v>13803</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>453</v>
+        <v>91</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="3">
-        <v>1329</v>
+        <v>13821</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>454</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="3">
-        <v>13303</v>
+        <v>13822</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>459</v>
+        <v>77</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="3">
-        <v>13304</v>
+        <v>13823</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="3">
-        <v>12345</v>
+        <v>13825</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>461</v>
+        <v>79</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="3">
-        <v>12346</v>
+        <v>14023</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>462</v>
+        <v>92</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="3">
-        <v>12114</v>
+        <v>14024</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>463</v>
+        <v>93</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="3">
-        <v>11217</v>
+        <v>14025</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>464</v>
+        <v>94</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="3">
-        <v>11218</v>
+        <v>14027</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>465</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A202" s="3">
+        <v>14121</v>
+      </c>
+      <c r="B202" s="24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" s="3">
+        <v>14122</v>
+      </c>
+      <c r="B203" s="24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" s="3">
+        <v>14123</v>
+      </c>
+      <c r="B204" s="24" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A205" s="3">
+        <v>14124</v>
+      </c>
+      <c r="B205" s="24" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A206" s="3">
+        <v>14125</v>
+      </c>
+      <c r="B206" s="24" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" s="3">
+        <v>14126</v>
+      </c>
+      <c r="B207" s="24" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A208" s="3">
+        <v>14127</v>
+      </c>
+      <c r="B208" s="24" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A209" s="3">
+        <v>14128</v>
+      </c>
+      <c r="B209" s="24" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B143">
-    <sortCondition ref="A1:A143"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B201">
+    <sortCondition ref="A1:A201"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD0C21E-1507-4FE6-8295-C92259A0C98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0ED394-F155-4904-98CB-5E1FE62B8401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="483">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5260,97 +5260,6 @@
   </si>
   <si>
     <t>潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×4(※2)(※3))</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級2人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級3人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級4人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級5人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級6人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級7人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>∞級8人専用コロシアム</t>
-    <rPh sb="0" eb="2">
-      <t>ムゲンキュウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>センヨウ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -7646,7 +7555,7 @@
     </row>
     <row r="31" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="22" t="s">
-        <v>472</v>
+        <v>395</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>397</v>
@@ -7684,7 +7593,7 @@
     </row>
     <row r="32" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="22" t="s">
-        <v>473</v>
+        <v>395</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>398</v>
@@ -7718,7 +7627,7 @@
     </row>
     <row r="33" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="22" t="s">
-        <v>474</v>
+        <v>395</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>399</v>
@@ -7754,7 +7663,7 @@
     </row>
     <row r="34" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="22" t="s">
-        <v>475</v>
+        <v>395</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>400</v>
@@ -7786,7 +7695,7 @@
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="22" t="s">
-        <v>476</v>
+        <v>395</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>401</v>
@@ -7820,7 +7729,7 @@
     </row>
     <row r="36" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="22" t="s">
-        <v>477</v>
+        <v>395</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>402</v>
@@ -7856,13 +7765,13 @@
     </row>
     <row r="37" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="22" t="s">
-        <v>478</v>
+        <v>395</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>422</v>
@@ -7874,7 +7783,7 @@
         <v>53</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="N37" s="23" t="s">
         <v>441</v>
@@ -9546,7 +9455,7 @@
         <v>14121</v>
       </c>
       <c r="B202" s="24" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9554,7 +9463,7 @@
         <v>14122</v>
       </c>
       <c r="B203" s="24" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9562,7 +9471,7 @@
         <v>14123</v>
       </c>
       <c r="B204" s="24" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9570,7 +9479,7 @@
         <v>14124</v>
       </c>
       <c r="B205" s="24" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9578,7 +9487,7 @@
         <v>14125</v>
       </c>
       <c r="B206" s="24" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9586,7 +9495,7 @@
         <v>14126</v>
       </c>
       <c r="B207" s="24" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9594,7 +9503,7 @@
         <v>14127</v>
       </c>
       <c r="B208" s="24" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9602,7 +9511,7 @@
         <v>14128</v>
       </c>
       <c r="B209" s="24" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0ED394-F155-4904-98CB-5E1FE62B8401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB870693-8293-4949-A959-8487FA9BCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
     <sheet name="素材名と図鑑番号の対応" sheetId="2" r:id="rId2"/>
-    <sheet name="お知らせ" sheetId="3" r:id="rId3"/>
-    <sheet name="メンテ期間" sheetId="4" r:id="rId4"/>
+    <sheet name="交換" sheetId="5" r:id="rId3"/>
+    <sheet name="お知らせ" sheetId="3" r:id="rId4"/>
+    <sheet name="メンテ期間" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="703">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -2544,67 +2545,6 @@
       <t>キョウチョウ</t>
     </rPh>
     <rPh sb="16" eb="17">
-      <t>シュウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>緋窮の億兆龍・アグリゲート, 蒼窮の億兆龍・アグリゲート,翠窮の億兆龍・アグリゲート,煌窮の億兆龍・アグリゲート,冥窮の億兆龍・アグリゲート：それぞれ約65周(最速で13周)</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>オクチョウリュウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>オクチョウリュウ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ミドリ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="32" eb="35">
-      <t>オクチョウリュウ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>キラ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>オクチョウリュウ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>オクチョウリュウ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>サイソク</t>
-    </rPh>
-    <rPh sb="85" eb="86">
       <t>シュウ</t>
     </rPh>
     <phoneticPr fontId="18"/>
@@ -4631,46 +4571,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>ゴクレグス：約230周,(※表示している値は平均をとったも。超デビルドラゴンの希石の偏りによってレートが増減する。(最低99周))</t>
-    <rPh sb="6" eb="7">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヘイキン</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>セキ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>カタヨ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ゾウゲン</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>サイテイ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>シュウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>龍現門(アグリゲート)：約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
     <rPh sb="0" eb="1">
       <t>リュウ</t>
@@ -5337,6 +5237,1809 @@
   </si>
   <si>
     <t>【スペード7】のトランプ兵,【ハート7】のトランプ兵,【ダイヤ7】のトランプ兵,【クラブ7】のトランプ兵,【ハート5】のトランプ兵,【ダイヤ4】のトランプ兵,【スペード3】のトランプ兵,【クラブ2】のトランプ兵(×3),潜在たまドラ☆HP強化++,潜在たまドラ☆攻撃強化++,潜在たまドラ☆回復強化++(×5),潜在たまドラ☆火ダメージ軽減+,潜在たまドラ☆水ダメージ軽減+,潜在たまドラ☆木ダメージ軽減+,潜在たまドラ☆光ダメージ軽減+,潜在たまドラ☆闇ダメージ軽減+(×5)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>交換先</t>
+    <rPh sb="0" eb="3">
+      <t>コウカンサキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>必要モンスター</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>条件</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>混沌の億兆龍</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>龍現門</t>
+    <rPh sb="0" eb="1">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>未知の新星ラッシュ</t>
+  </si>
+  <si>
+    <t>裏未知の新星ラッシュ</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
+  </si>
+  <si>
+    <t>すべて</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約550周,(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低495周))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏混沌の億兆龍</t>
+    <rPh sb="0" eb="1">
+      <t>ウラ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>龍現門</t>
+    <rPh sb="0" eb="3">
+      <t>リュウゲンモン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎天双極星・イフリートの希石(×99),水天双極星・リヴァイアサンの希石(×99),風天双極星・ファフニールの希石(×99),光天双極星・神龍の希石(×99),闇天双極星・ティアマットの希石(×99)</t>
+  </si>
+  <si>
+    <t>炎天双極星・イフリートの希石(×99),水天双極星・リヴァイアサンの希石(×99),風天双極星・ファフニールの希石(×99),光天双極星・神龍の希石(×99),闇天双極星・ティアマットの希石(×99)</t>
+    <rPh sb="0" eb="4">
+      <t>エンテンソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>スイテン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ソウキョクホシ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>シンリュウ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎天双極星・イフリートの希石</t>
+    <rPh sb="0" eb="2">
+      <t>エンテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水天双極星・リヴァイアサンの希石</t>
+    <rPh sb="0" eb="5">
+      <t>スイテンソウキョクホシ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風天双極星・ファフニールの希石</t>
+    <rPh sb="0" eb="1">
+      <t>フウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>光天双極星・神龍の希石</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウキョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンリュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇天双極星・ティアマットの希石</t>
+    <rPh sb="0" eb="5">
+      <t>ヤミテンソウキョクホシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏極悪生命体</t>
+  </si>
+  <si>
+    <t>極悪生命体</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴクレグス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴクレグス：約230周,(※表示している値は平均をとったもの。超デビルドラゴンの希石の偏りによってレートが増減する。(最低99周))</t>
+    <rPh sb="6" eb="7">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>カタヨ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ゾウゲン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約230周,(※表示している値は平均をとったもの。超デビルドラゴンの希石の偏りによってレートが増減する。(最低99周))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグスの希石(×99),超バジリスクの希石(×99),超デビルドラゴンの希石(×20)</t>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグスの希石(×99),超バジリスクの希石(×99),超デビルドラゴンの希石(×20)</t>
+    <rPh sb="0" eb="5">
+      <t>ゴクアクセイメイタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゴクレグス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百龍</t>
+  </si>
+  <si>
+    <t>煉燼の百式龍・ビャクレンコウ</t>
+  </si>
+  <si>
+    <t>50周</t>
+  </si>
+  <si>
+    <t>50周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煉燼の百式龍・ビャクレンコウ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>浄罪の千龍</t>
+  </si>
+  <si>
+    <t>浄罪の千手龍・センキョウ</t>
+  </si>
+  <si>
+    <t>浄罪の千手龍・センキョウ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万龍</t>
+  </si>
+  <si>
+    <t>百式龍・ビャクレンコウ</t>
+    <rPh sb="0" eb="3">
+      <t>ヒャクシキリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>百式龍・ビャクレンコウ(×5),煉燼の百式龍・ビャクレンコウの希石(×50),火の希石【巨大】(×30),レッドドラゴンフルーツ(×50),ドラゴンフラワー(×50)</t>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドラゴンフラワー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レッドドラゴンフルーツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>千手龍・センキョウ(×5),浄罪の千手龍・センキョウの希石(×50),水の希石【巨大】(×30),ブルードラゴンフルーツ(×50),ドラゴンプラント(×50)</t>
+    <rPh sb="0" eb="2">
+      <t>センテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>千手龍・センキョウ</t>
+    <rPh sb="0" eb="3">
+      <t>センテリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ブルードラゴンフルーツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドラゴンプラント</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万寿龍・クーバンシェン</t>
+  </si>
+  <si>
+    <t>万寿龍・クーバンシェン(×5),深遠の万寿龍・クーバンシェンの希石(×50),木の希石【巨大】(×30),グリーンドラゴンフルーツ(×50),ドラゴンシード(×50)</t>
+    <rPh sb="0" eb="3">
+      <t>マンジュリュウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>万寿龍・クーバンシェン</t>
+    <rPh sb="0" eb="3">
+      <t>マンジュリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グリーンドラゴンフルーツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドラゴンシード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アームズシーカー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>銀翼の白迅帝</t>
+  </si>
+  <si>
+    <t>20周</t>
+  </si>
+  <si>
+    <t>ディープシーカーの左腕の希石(×20),ディープシーカーの右腕の希石(×20)</t>
+    <rPh sb="9" eb="11">
+      <t>ヒダリウデ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ミギウデ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>星砕の兆龍</t>
+  </si>
+  <si>
+    <t>星砕の凶兆龍・ゼンチョウガ</t>
+  </si>
+  <si>
+    <t>凶兆龍・ゼンチョウガ(×5),星砕の凶兆龍・ゼンチョウガの希石(×50),闇の希石【巨大】(×30),ダイヤドラゴンフルーツ(×25),ドラゴンフルーツ(×50)</t>
+    <rPh sb="0" eb="3">
+      <t>キョウチョウリュウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>凶兆龍・ゼンチョウガ</t>
+    <rPh sb="0" eb="3">
+      <t>キョウチョウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドラゴンフルーツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約65周(最速13周)</t>
+  </si>
+  <si>
+    <t>約65周(最速13周)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>伍窮の億兆龍</t>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲート</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冥窮の億兆龍・アグリゲート</t>
+  </si>
+  <si>
+    <t>冥窮の億兆龍・アグリゲート</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲート</t>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲート,蒼窮の億兆龍・アグリゲート,翠窮の億兆龍・アグリゲート,煌窮の億兆龍・アグリゲート,冥窮の億兆龍・アグリゲート：それぞれ約65周(最速で13周)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>キラ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>サイソク</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼窮の億兆龍・アグリゲート</t>
+  </si>
+  <si>
+    <t>翠窮の億兆龍・アグリゲート</t>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲート</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>煌窮の億兆龍・アグリゲートの希石(×50),光の希石【巨大】(×30),光の希石【特大】(×50),ダイヤドラゴンフルーツ(×25),ドラゴンシード(×50)</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冥窮の億兆龍・アグリゲートの希石(×50),闇の希石【巨大】(×30),闇の希石【特大】(×50),ダイヤドラゴンフルーツ(×25),ドラゴンプラント(×50)</t>
+    <rPh sb="22" eb="23">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヤミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>緋窮の億兆龍・アグリゲートの希石(×50),火の希石【巨大】(×30),火の希石【特大】(×50),レッドドラゴンフルーツ(×50),ドラゴンシード(×50)</t>
+    <rPh sb="22" eb="23">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼窮の億兆龍・アグリゲート</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>蒼窮の億兆龍・アグリゲートの希石(×50),水の希石【巨大】(×30),水の希石【特大】(×50),ブルードラゴンフルーツ(×50),ドラゴンプラント(×50)</t>
+    <rPh sb="22" eb="23">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>翠窮の億兆龍・アグリゲート</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>翠窮の億兆龍・アグリゲートの希石(×50),木の希石【巨大】(×30),木の希石【特大】(×50),グリーンドラゴンフルーツ(×50),ドラゴンフラワー(×50)</t>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の薙刀</t>
+  </si>
+  <si>
+    <t>巴御前の薙刀</t>
+    <rPh sb="0" eb="3">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタナ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の強弓</t>
+    <rPh sb="0" eb="3">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ユミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天境の白霹竜</t>
+  </si>
+  <si>
+    <t>10周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の希石(×10)</t>
+    <rPh sb="0" eb="3">
+      <t>トモエゴゼン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>深遠の万寿龍・クーバンシェン</t>
+    <rPh sb="0" eb="2">
+      <t>シンエン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>マンジュリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アームズシーカー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>巴御前の強弓</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグス</t>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体</t>
+  </si>
+  <si>
+    <t>フリングホルニ</t>
+  </si>
+  <si>
+    <t>20周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フリングホルニ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フリングホルニの希石(×20)</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>デビリット</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モリりんのカード</t>
+  </si>
+  <si>
+    <t>モリりんのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ワルりんのカード</t>
+  </si>
+  <si>
+    <t>ワルりんのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>裏未知の新星ラッシュ</t>
+  </si>
+  <si>
+    <t>ルウのおとも・モリりんの希石(×20)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ルウのおとも・ワルりんの希石(×20)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリス</t>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリス</t>
+    <rPh sb="0" eb="2">
+      <t>モクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>25周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジュピトールのプラネットハンマー</t>
+  </si>
+  <si>
+    <t>ジュピトールのプラネットハンマー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の希石(×50)</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・アスタロトの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>予見の魔神将・アスタロトのカード</t>
+  </si>
+  <si>
+    <t>予見の魔神将・アスタロトのカード</t>
+    <rPh sb="0" eb="2">
+      <t>ヨケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>古代の碧神面</t>
+  </si>
+  <si>
+    <t>森の番人</t>
+    <rPh sb="0" eb="1">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>炎の番人</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暴乱の極悪生命体・ゴクレグスの希石(×50),火の希石【巨大】(×30),闇の希石【特大】(×50),炎の番人(×50),デビリット(×50)</t>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トクダイ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木星の守霊・ユーピリスの希石(×50),木星の魔導神機・ジュピトールの希石(×50),木の希石【巨大】(×50),古代の碧神面(×50),森の番人(×50)</t>
+    <rPh sb="43" eb="44">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヘキ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守霊・メルキス</t>
+  </si>
+  <si>
+    <t>水星の守霊・メルキス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>99周</t>
+  </si>
+  <si>
+    <t>99周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守霊・メルキスの希石(×99),水星の守護聖霊・マーキュリアの希石(×50),水星の希石(×50),水の希石【特大】(×50),古代の蒼神面(×50)</t>
+    <rPh sb="42" eb="44">
+      <t>スイセイ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>トクダイ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マーキュリアのプラネットランス</t>
+  </si>
+  <si>
+    <t>マーキュリアのプラネットランス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水星の守護者</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マーキュリアのプラネットランスの希石(×99),水星の希石(×50)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>義侠の魔神将・アモンのカード</t>
+  </si>
+  <si>
+    <t>義侠の魔神将・アモンのカード</t>
+    <rPh sb="0" eb="1">
+      <t>ギ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・アモンの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>古代の蒼神面</t>
+    <rPh sb="3" eb="4">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守霊・ハクレイ</t>
+  </si>
+  <si>
+    <t>金星の守霊・ハクレイ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>タイハクセイの七星剣</t>
+  </si>
+  <si>
+    <t>閃剣の魔神将・バアルのカード</t>
+  </si>
+  <si>
+    <t>閃剣の魔神将・バアルのカード</t>
+    <rPh sb="0" eb="1">
+      <t>ヒラメ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マジン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>タイハクセイの七星剣の希石(×99),金星の希石(×99)</t>
+    <rPh sb="19" eb="21">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・バアルの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金星の守霊・ハクレイの希石(×99),金星の守護星獣・タイハクセイの希石(×50),金星の希石(×50),光の希石【巨大】(×50),黄金の番人(×50)</t>
+    <rPh sb="42" eb="44">
+      <t>キンセイ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>オウゴン</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>タイハクセイの七星剣</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>黄金の番人</t>
+    <rPh sb="0" eb="2">
+      <t>オウゴン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守霊・メレナ</t>
+  </si>
+  <si>
+    <t>月の守霊・メレナ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守霊・メレナの希石(×99),月の守護妖魔・セレナディアの希石(×50),月の希石(×50),闇の希石【巨大】(×50),虹の番人(×50)</t>
+    <rPh sb="39" eb="40">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ニジ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>バンニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>月の守護妖魔・セレナディアの希石(×50),月の希石(×50)</t>
+  </si>
+  <si>
+    <t>セレナディアの双月棍</t>
+  </si>
+  <si>
+    <t>セレナディアの双月棍</t>
+    <rPh sb="7" eb="8">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>逆心の神魔王・ルシファーのカード</t>
+  </si>
+  <si>
+    <t>逆心の神魔王・ルシファーのカード</t>
+    <rPh sb="0" eb="2">
+      <t>ギャクシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マオウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソフィの召喚・ルシファーの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>虹の番人</t>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚</t>
+  </si>
+  <si>
+    <t>ミゲイルの冥堕鎚</t>
+  </si>
+  <si>
+    <t>冥境の黒熾龍</t>
+  </si>
+  <si>
+    <t>30周</t>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚の希石(×30)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの冥堕鎚の希石(×30)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの岩砕鎚</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ミゲイルの冥堕鎚</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディー</t>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守護者</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>太陽の守霊・ソルディーの希石(×99),太陽の守護星龍・サンドルムの希石(×50),太陽の希石(×50),火の希石【巨大】(×50),レッドドラゴンフルーツ(×50)</t>
+    <rPh sb="42" eb="44">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サンドルムの烈火輪の希石(×99),太陽の希石(×50)</t>
+    <rPh sb="18" eb="20">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サンドルムの烈火輪</t>
+  </si>
+  <si>
+    <t>邪炎の魔神将・ベリアルのカード</t>
+  </si>
+  <si>
+    <t>ソフィの召喚・ベリアルの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サンドルムの烈火輪</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>邪炎の魔神将・ベリアルのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風雲龍王・ネフェル&amp;アネモス</t>
+  </si>
+  <si>
+    <t>風雲龍王・ネフェル&amp;アネモス</t>
+    <rPh sb="0" eb="4">
+      <t>フウウンリュウオウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>風雲の龍王</t>
+  </si>
+  <si>
+    <t>200周</t>
+    <rPh sb="3" eb="4">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>べりドラのカード</t>
+  </si>
+  <si>
+    <t>双嵐の風雲龍王・ネフェル&amp;アネモスの希石(×200),アネモスの剣の希石(×99),ネフェルの盾の希石(×99),水の希石【巨大】(×50),木の希石【巨大】(×50)</t>
+    <rPh sb="57" eb="58">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アネモスの剣の希石(×99),ネフェルの盾の希石(×99)</t>
+  </si>
+  <si>
+    <t>ブルッカのおとも・べりドラの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>必要周回数</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュウカイスウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アネモスの剣&amp;ネフェルの盾</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>べりドラのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アネモスの剣&amp;ネフェルの盾</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅蓮の機王</t>
+  </si>
+  <si>
+    <t>紅蓮機王・ヴォルガント</t>
+  </si>
+  <si>
+    <t>ヴォルガントのヴォルカニックランス</t>
+  </si>
+  <si>
+    <t>神器に宿る者・ガリヴァン</t>
+  </si>
+  <si>
+    <t>ヴォルガントの槍の希石(×99),ヴォルガントの盾の希石(×99)</t>
+  </si>
+  <si>
+    <t>火山の紅蓮機王・ヴォルガントの希石(×200),ヴォルガントの槍の希石(×99),ヴォルガントの盾の希石(×99),火の希石【巨大】(×50),木の希石【巨大】(×50)</t>
+    <rPh sb="58" eb="59">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神器に宿る者・ガリヴァンの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅蓮機王・ヴォルガント</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヴォルガントのヴォルカニックランス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神器に宿る者・ガリヴァン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>霧雨魔王・グレゴウル</t>
+  </si>
+  <si>
+    <t>霧雨の魔王</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレゴウルの魔剣ミスティレイン</t>
+  </si>
+  <si>
+    <t>ぶどドラのカード</t>
+  </si>
+  <si>
+    <t>黒雲の霧雨魔王・グレゴウルの希石(×200),グレゴウルの魔剣ミスティレインの希石(×99),グレゴウルの翼の希石(×99),闇の希石【巨大】(×50),水の希石【巨大】(×50)</t>
+    <rPh sb="63" eb="64">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレゴウルの魔剣ミスティレインの希石(×99),グレゴウルの翼の希石(×99)</t>
+  </si>
+  <si>
+    <t>グレーシスのおとも・ぶどドラの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>グレゴウルの魔剣ミスティレイン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>霧雨魔王・グレゴウル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ぶどドラのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大樹霊王・アドネア</t>
+  </si>
+  <si>
+    <t>神器に宿る者・グラオル</t>
+  </si>
+  <si>
+    <t>大樹の霊王</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宿木の大樹霊王・アドネアの希石(×200),宿木の大樹霊王・アドネアの左根の希石(×99),宿木の大樹霊王・アドネアの右根の希石(×99),木の希石【巨大】(×50),水の希石【巨大】(×50)</t>
+    <rPh sb="59" eb="60">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>宿木の大樹霊王・アドネアの左根の希石(×99),宿木の大樹霊王・アドネアの右根の希石(×99)</t>
+  </si>
+  <si>
+    <t>神器に宿る者・グラオルの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大樹霊王・アドネア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アドネアの樹霊根</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神器に宿る者・グラオル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アドネアの樹霊根</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天穹神王・アレクセン</t>
+  </si>
+  <si>
+    <t>アレクセンの王笏アトモスワンダー</t>
+  </si>
+  <si>
+    <t>れもドラのカード</t>
+  </si>
+  <si>
+    <t>天穹の神王</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>虹耀の天穹神王・アレクセンの希石(×200),アレクセンの聖鳥の希石(×99),アレクセンの翼の希石(×99),光の希石【巨大】(×100)</t>
+    <rPh sb="56" eb="57">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>キョダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アレクセンの聖鳥の希石(×99),アレクセンの翼の希石(×99)</t>
+  </si>
+  <si>
+    <t>レモックのおとも・れもドラの希石(×25)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アレクセンの王笏アトモスワンダー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天穹神王・アレクセン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>れもドラのカード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>火の希石【特大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>水の希石【特大】</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>木の希石【特大】</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>光の希石【特大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>闇の希石【特大】</t>
+    <rPh sb="0" eb="1">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクダイ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -6088,11 +7791,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -6503,13 +8206,13 @@
         <v>31</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>36</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>10</v>
@@ -6568,7 +8271,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>98</v>
@@ -6628,7 +8331,7 @@
         <v>25</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>18</v>
@@ -6642,7 +8345,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>3</v>
+        <v>669</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>100</v>
@@ -6682,7 +8385,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>4</v>
+        <v>691</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>101</v>
@@ -6820,7 +8523,7 @@
         <v>170</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>171</v>
@@ -6920,27 +8623,27 @@
         <v>213</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="F12" s="10">
         <v>2970</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -6956,10 +8659,10 @@
         <v>214</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="F13" s="10">
         <v>2970</v>
@@ -6967,14 +8670,14 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
@@ -6990,27 +8693,27 @@
         <v>215</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F14" s="10">
         <v>2970</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
@@ -7026,27 +8729,27 @@
         <v>216</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="F15" s="10">
         <v>6600</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -7059,36 +8762,36 @@
         <v>211</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>217</v>
+        <v>546</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F16" s="10">
         <v>5555</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K16" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>267</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -7099,51 +8802,51 @@
         <v>212</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>276</v>
       </c>
       <c r="F17" s="10">
         <v>7777</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>272</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>273</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N17" s="21" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="F18" s="10">
         <v>2970</v>
@@ -7151,91 +8854,91 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>326</v>
       </c>
       <c r="K18" s="12"/>
       <c r="L18" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>335</v>
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>299</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>340</v>
       </c>
       <c r="K20" s="12"/>
       <c r="L20" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>301</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>302</v>
       </c>
       <c r="F21" s="10">
         <v>2970</v>
@@ -7243,33 +8946,33 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>344</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>345</v>
       </c>
       <c r="K21" s="12"/>
       <c r="L21" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>304</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>305</v>
       </c>
       <c r="F22" s="10">
         <v>2970</v>
@@ -7277,31 +8980,31 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
       <c r="L22" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>307</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>308</v>
       </c>
       <c r="F23" s="10">
         <v>2970</v>
@@ -7309,31 +9012,31 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
       <c r="L23" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="M23" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>381</v>
       </c>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F24" s="10">
         <v>2970</v>
@@ -7341,29 +9044,29 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
       <c r="L24" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F25" s="10">
         <v>2970</v>
@@ -7371,31 +9074,31 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F26" s="10">
         <v>2970</v>
@@ -7403,31 +9106,31 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K26" s="12"/>
       <c r="L26" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>315</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>316</v>
       </c>
       <c r="F27" s="10">
         <v>2970</v>
@@ -7435,211 +9138,211 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K27" s="12"/>
       <c r="L27" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="F28" s="10">
         <v>2970</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
       <c r="L28" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>321</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F29" s="10">
         <v>7777</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
       <c r="L29" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>396</v>
-      </c>
       <c r="C30" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="K31" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>433</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>435</v>
       </c>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>404</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>405</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>407</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>408</v>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L32" s="12"/>
       <c r="M32" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>410</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>411</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -7647,101 +9350,101 @@
         <v>30</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L33" s="12"/>
       <c r="M33" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="N33" s="11" t="s">
         <v>440</v>
-      </c>
-      <c r="N33" s="11" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J34" s="12"/>
       <c r="K34" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
       <c r="N34" s="11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>419</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
       <c r="M35" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>420</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>422</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
@@ -7749,44 +9452,50 @@
         <v>30</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J36" s="12"/>
       <c r="K36" s="11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L36" s="12"/>
       <c r="M36" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="H37" s="15">
+        <v>394</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9">
         <v>30</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="23" t="s">
-        <v>482</v>
-      </c>
-      <c r="N37" s="23" t="s">
-        <v>441</v>
+      <c r="L37" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="M37" s="12"/>
+      <c r="N37" s="11" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -7835,7 +9544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -7855,7 +9564,7 @@
         <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -7863,7 +9572,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -7871,1652 +9580,2276 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3">
-        <v>322</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>347</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>348</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>349</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
-        <v>325</v>
+        <v>153</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>350</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
-        <v>326</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>352</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>353</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>354</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
-        <v>1077</v>
+        <v>335</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>62</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
-        <v>1081</v>
+        <v>336</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>75</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
-        <v>1083</v>
+        <v>337</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
-        <v>1095</v>
+        <v>338</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
-        <v>1096</v>
+        <v>339</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
-        <v>1109</v>
+        <v>340</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
-        <v>1110</v>
+        <v>341</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
-        <v>1111</v>
+        <v>916</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>370</v>
+        <v>573</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
-        <v>1325</v>
+        <v>1077</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>450</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
-        <v>1326</v>
+        <v>1081</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>451</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
-        <v>1327</v>
+        <v>1083</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>452</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
-        <v>1328</v>
+        <v>1085</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>453</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
-        <v>1329</v>
+        <v>1086</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>454</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
-        <v>1340</v>
+        <v>1087</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>387</v>
+        <v>528</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
-        <v>1341</v>
+        <v>1095</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>224</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3">
-        <v>1547</v>
+        <v>1096</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>177</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3">
-        <v>1548</v>
+        <v>1109</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3">
-        <v>1549</v>
+        <v>1110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>179</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3">
-        <v>1550</v>
+        <v>1111</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>180</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3">
-        <v>1551</v>
+        <v>1176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>181</v>
+        <v>617</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3">
-        <v>1709</v>
+        <v>1294</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>58</v>
+        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3">
-        <v>2250</v>
+        <v>1295</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>61</v>
+        <v>590</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3">
-        <v>2425</v>
+        <v>1325</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3">
-        <v>3317</v>
+        <v>1326</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>136</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3">
-        <v>3318</v>
+        <v>1327</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>227</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3">
-        <v>3319</v>
+        <v>1328</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>228</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3">
-        <v>3320</v>
+        <v>1329</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3">
-        <v>3321</v>
+        <v>1340</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>386</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3">
-        <v>3322</v>
+        <v>1341</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3">
-        <v>3323</v>
+        <v>1547</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3">
-        <v>3324</v>
+        <v>1548</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3">
-        <v>3325</v>
+        <v>1549</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>234</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3">
-        <v>3700</v>
+        <v>1550</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3">
-        <v>3701</v>
+        <v>1551</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3">
-        <v>3702</v>
+        <v>1709</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3">
-        <v>3795</v>
+        <v>2250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3">
-        <v>3826</v>
+        <v>2425</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>446</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3">
-        <v>3827</v>
+        <v>3317</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3">
-        <v>3891</v>
+        <v>3318</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>60</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3">
-        <v>3911</v>
+        <v>3319</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>55</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
-        <v>3971</v>
+        <v>3320</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>56</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
-        <v>3973</v>
+        <v>3321</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
-        <v>3974</v>
+        <v>3322</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>137</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
-        <v>4014</v>
+        <v>3323</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
-        <v>4369</v>
+        <v>3324</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
-        <v>4370</v>
+        <v>3325</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>49</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
-        <v>4371</v>
+        <v>3700</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3">
-        <v>4372</v>
+        <v>3701</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3">
-        <v>4373</v>
+        <v>3702</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3">
-        <v>5739</v>
+        <v>3795</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3">
-        <v>6073</v>
+        <v>3826</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>158</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3">
-        <v>6074</v>
+        <v>3827</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>159</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3">
-        <v>6075</v>
+        <v>3891</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3">
-        <v>6076</v>
+        <v>3911</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3">
-        <v>6077</v>
+        <v>3971</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3">
-        <v>6178</v>
+        <v>3973</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3">
-        <v>6522</v>
+        <v>3974</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>252</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
-        <v>6607</v>
+        <v>4014</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
-        <v>6608</v>
+        <v>4369</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
-        <v>6609</v>
+        <v>4370</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
-        <v>6878</v>
+        <v>4371</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>251</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
-        <v>7020</v>
+        <v>4372</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
-        <v>7021</v>
+        <v>4373</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
-        <v>7022</v>
+        <v>5739</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
-        <v>7023</v>
+        <v>6073</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
-        <v>7042</v>
+        <v>6074</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
-        <v>7493</v>
+        <v>6075</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>253</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
-        <v>7680</v>
+        <v>6076</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>327</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
-        <v>7681</v>
+        <v>6077</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>328</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
-        <v>7684</v>
+        <v>6178</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>329</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
-        <v>7686</v>
+        <v>6522</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>330</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
-        <v>8298</v>
+        <v>6607</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
-        <v>8551</v>
+        <v>6608</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
-        <v>8552</v>
+        <v>6609</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
-        <v>8553</v>
+        <v>6878</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
-        <v>8554</v>
+        <v>7020</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>280</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
-        <v>8555</v>
+        <v>7021</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>281</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
-        <v>8728</v>
+        <v>7022</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
-        <v>8914</v>
+        <v>7023</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>323</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
-        <v>8916</v>
+        <v>7042</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>324</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
-        <v>9000</v>
+        <v>7493</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>66</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
-        <v>9227</v>
+        <v>7680</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3">
-        <v>9229</v>
+        <v>7681</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
-        <v>9454</v>
+        <v>7684</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>67</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
-        <v>9455</v>
+        <v>7686</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
-        <v>9457</v>
+        <v>7757</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>338</v>
+        <v>698</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
-        <v>9534</v>
+        <v>7758</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>166</v>
+        <v>699</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
-        <v>9716</v>
+        <v>7759</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>342</v>
+        <v>700</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3">
-        <v>9827</v>
+        <v>7760</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>343</v>
+        <v>701</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3">
-        <v>10022</v>
+        <v>7761</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>70</v>
+        <v>702</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3">
-        <v>10023</v>
+        <v>8298</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3">
-        <v>10024</v>
+        <v>8551</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3">
-        <v>10025</v>
+        <v>8552</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>73</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3">
-        <v>10026</v>
+        <v>8553</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>74</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3">
-        <v>10114</v>
+        <v>8554</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3">
-        <v>10512</v>
+        <v>8555</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>140</v>
+        <v>280</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3">
-        <v>10513</v>
+        <v>8728</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3">
-        <v>10514</v>
+        <v>8914</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>150</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3">
-        <v>10515</v>
+        <v>8915</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>182</v>
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3">
-        <v>10516</v>
+        <v>8916</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>168</v>
+        <v>323</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3">
-        <v>10517</v>
+        <v>9000</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3">
-        <v>10518</v>
+        <v>9227</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>151</v>
+        <v>331</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3">
-        <v>10519</v>
+        <v>9228</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>141</v>
+        <v>522</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3">
-        <v>10520</v>
+        <v>9229</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>169</v>
+        <v>332</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3">
-        <v>10521</v>
+        <v>9454</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3">
-        <v>10528</v>
+        <v>9455</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>129</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3">
-        <v>10529</v>
+        <v>9456</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>130</v>
+        <v>527</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3">
-        <v>10530</v>
+        <v>9457</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>131</v>
+        <v>337</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3">
-        <v>10533</v>
+        <v>9534</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="3">
-        <v>11037</v>
+        <v>9716</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="3">
-        <v>11038</v>
+        <v>9718</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>378</v>
+        <v>537</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="3">
-        <v>11039</v>
+        <v>9827</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="3">
-        <v>11040</v>
+        <v>9870</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>376</v>
+        <v>492</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="3">
-        <v>11046</v>
+        <v>10007</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>374</v>
+        <v>495</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="3">
-        <v>11108</v>
+        <v>10008</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>167</v>
+        <v>496</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="3">
-        <v>11119</v>
+        <v>10009</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>223</v>
+        <v>497</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="3">
-        <v>11196</v>
+        <v>10010</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>240</v>
+        <v>498</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="3">
-        <v>11207</v>
+        <v>10011</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>244</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="3">
-        <v>11217</v>
+        <v>10022</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>464</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="3">
-        <v>11218</v>
+        <v>10023</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>465</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="3">
-        <v>11552</v>
+        <v>10024</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>245</v>
+        <v>72</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="3">
-        <v>11556</v>
+        <v>10025</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>257</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="3">
-        <v>11559</v>
+        <v>10026</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="3">
-        <v>11562</v>
+        <v>10114</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>259</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="3">
-        <v>11565</v>
+        <v>10297</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>260</v>
+        <v>507</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="3">
-        <v>11568</v>
+        <v>10512</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>261</v>
+        <v>140</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="3">
-        <v>11588</v>
+        <v>10513</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="3">
-        <v>12114</v>
+        <v>10514</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>463</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="3">
-        <v>12257</v>
+        <v>10515</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>268</v>
+        <v>182</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="3">
-        <v>12258</v>
+        <v>10516</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>270</v>
+        <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="3">
-        <v>12261</v>
+        <v>10517</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="3">
-        <v>12345</v>
+        <v>10518</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>461</v>
+        <v>151</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="3">
-        <v>12346</v>
+        <v>10519</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>462</v>
+        <v>141</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="3">
-        <v>12691</v>
+        <v>10520</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="3">
-        <v>12692</v>
+        <v>10521</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="3">
-        <v>12693</v>
+        <v>10522</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>144</v>
+        <v>581</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="3">
-        <v>12696</v>
+        <v>10528</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="3">
-        <v>12697</v>
+        <v>10529</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="3">
-        <v>12863</v>
+        <v>10530</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="3">
-        <v>12864</v>
+        <v>10531</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>154</v>
+        <v>584</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="3">
-        <v>12865</v>
+        <v>10532</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>155</v>
+        <v>588</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="3">
-        <v>12866</v>
+        <v>10533</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="3">
-        <v>12869</v>
+        <v>11037</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>157</v>
+        <v>376</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="3">
-        <v>13047</v>
+        <v>11038</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>443</v>
+        <v>377</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="3">
-        <v>13048</v>
+        <v>11039</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>444</v>
+        <v>374</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="3">
-        <v>13055</v>
+        <v>11040</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>173</v>
+        <v>375</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="3">
-        <v>13056</v>
+        <v>11046</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>174</v>
+        <v>373</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="3">
-        <v>13057</v>
+        <v>11108</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="3">
-        <v>13060</v>
+        <v>11115</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>176</v>
+        <v>509</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="3">
-        <v>13295</v>
+        <v>11119</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="3">
-        <v>13303</v>
+        <v>11192</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>459</v>
+        <v>514</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="3">
-        <v>13304</v>
+        <v>11196</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>460</v>
+        <v>239</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="3">
-        <v>13381</v>
+        <v>11203</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>189</v>
+        <v>563</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="3">
-        <v>13382</v>
+        <v>11207</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="3">
-        <v>13383</v>
+        <v>11216</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>191</v>
+        <v>564</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="3">
-        <v>13384</v>
+        <v>11217</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>192</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="3">
-        <v>13499</v>
+        <v>11218</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>84</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="3">
-        <v>13500</v>
+        <v>11548</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>85</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="3">
-        <v>13501</v>
+        <v>11552</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="3">
-        <v>13503</v>
+        <v>11553</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>87</v>
+        <v>542</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="3">
-        <v>13590</v>
+        <v>11556</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>80</v>
+        <v>256</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="3">
-        <v>13591</v>
+        <v>11557</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>81</v>
+        <v>543</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="3">
-        <v>13592</v>
+        <v>11559</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>82</v>
+        <v>257</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="3">
-        <v>13594</v>
+        <v>11560</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>83</v>
+        <v>545</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="3">
-        <v>13667</v>
+        <v>11562</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>64</v>
+        <v>258</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="3">
-        <v>13799</v>
+        <v>11563</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>88</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="3">
-        <v>13800</v>
+        <v>11565</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>89</v>
+        <v>259</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="3">
-        <v>13801</v>
+        <v>11566</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>90</v>
+        <v>548</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="3">
-        <v>13803</v>
+        <v>11568</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>91</v>
+        <v>260</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="3">
-        <v>13821</v>
+        <v>11588</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>76</v>
+        <v>245</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="3">
-        <v>13822</v>
+        <v>12112</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>77</v>
+        <v>565</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="3">
-        <v>13823</v>
+        <v>12113</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>78</v>
+        <v>557</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="3">
-        <v>13825</v>
+        <v>12114</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>79</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="3">
-        <v>14023</v>
+        <v>12252</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>92</v>
+        <v>566</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="3">
-        <v>14024</v>
+        <v>12257</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>93</v>
+        <v>267</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="3">
-        <v>14025</v>
+        <v>12258</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>94</v>
+        <v>269</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="3">
-        <v>14027</v>
+        <v>12260</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>95</v>
+        <v>568</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="3">
-        <v>14121</v>
-      </c>
-      <c r="B202" s="24" t="s">
-        <v>474</v>
+        <v>12261</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="3">
-        <v>14122</v>
-      </c>
-      <c r="B203" s="24" t="s">
-        <v>475</v>
+        <v>12343</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="3">
-        <v>14123</v>
-      </c>
-      <c r="B204" s="24" t="s">
-        <v>476</v>
+        <v>12344</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="3">
-        <v>14124</v>
-      </c>
-      <c r="B205" s="24" t="s">
-        <v>477</v>
+        <v>12345</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="3">
-        <v>14125</v>
-      </c>
-      <c r="B206" s="24" t="s">
-        <v>478</v>
+        <v>12346</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="3">
-        <v>14126</v>
-      </c>
-      <c r="B207" s="24" t="s">
-        <v>479</v>
+        <v>12685</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="3">
-        <v>14127</v>
-      </c>
-      <c r="B208" s="24" t="s">
-        <v>480</v>
+        <v>12691</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="3">
+        <v>12692</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A210" s="3">
+        <v>12693</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A211" s="3">
+        <v>12694</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A212" s="3">
+        <v>12695</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A213" s="3">
+        <v>12696</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A214" s="3">
+        <v>12697</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" s="3">
+        <v>12857</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A216" s="3">
+        <v>12863</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A217" s="3">
+        <v>12864</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A218" s="3">
+        <v>12865</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" s="3">
+        <v>12866</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A220" s="3">
+        <v>12867</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A221" s="3">
+        <v>12868</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A222" s="3">
+        <v>12869</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A223" s="3">
+        <v>13047</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A224" s="3">
+        <v>13048</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A225" s="3">
+        <v>13049</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A226" s="3">
+        <v>13055</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A227" s="3">
+        <v>13056</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A228" s="3">
+        <v>13057</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A229" s="3">
+        <v>13058</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A230" s="3">
+        <v>13059</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A231" s="3">
+        <v>13060</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A232" s="3">
+        <v>13294</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A233" s="3">
+        <v>13295</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A234" s="3">
+        <v>13301</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A235" s="3">
+        <v>13302</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A236" s="3">
+        <v>13303</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A237" s="3">
+        <v>13304</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A238" s="3">
+        <v>13375</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A239" s="3">
+        <v>13381</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A240" s="3">
+        <v>13382</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A241" s="3">
+        <v>13383</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A242" s="3">
+        <v>13384</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A243" s="3">
+        <v>13385</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A244" s="3">
+        <v>13494</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A245" s="3">
+        <v>13498</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A246" s="3">
+        <v>13499</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A247" s="3">
+        <v>13500</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A248" s="3">
+        <v>13501</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A249" s="3">
+        <v>13502</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A250" s="3">
+        <v>13503</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A251" s="3">
+        <v>13585</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A252" s="3">
+        <v>13589</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A253" s="3">
+        <v>13590</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A254" s="3">
+        <v>13591</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A255" s="3">
+        <v>13592</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A256" s="3">
+        <v>13593</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A257" s="3">
+        <v>13594</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A258" s="3">
+        <v>13667</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A259" s="3">
+        <v>13794</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A260" s="3">
+        <v>13798</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A261" s="3">
+        <v>13799</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A262" s="3">
+        <v>13800</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A263" s="3">
+        <v>13801</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A264" s="3">
+        <v>13802</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A265" s="3">
+        <v>13803</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A266" s="3">
+        <v>13816</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A267" s="3">
+        <v>13820</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A268" s="3">
+        <v>13821</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A269" s="3">
+        <v>13822</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A270" s="3">
+        <v>13823</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A271" s="3">
+        <v>13824</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A272" s="3">
+        <v>13825</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A273" s="3">
+        <v>14018</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A274" s="3">
+        <v>14022</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A275" s="3">
+        <v>14023</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A276" s="3">
+        <v>14024</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A277" s="3">
+        <v>14025</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A278" s="3">
+        <v>14026</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A279" s="3">
+        <v>14027</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A280" s="3">
+        <v>14121</v>
+      </c>
+      <c r="B280" s="23" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A281" s="3">
+        <v>14122</v>
+      </c>
+      <c r="B281" s="23" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A282" s="3">
+        <v>14123</v>
+      </c>
+      <c r="B282" s="23" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A283" s="3">
+        <v>14124</v>
+      </c>
+      <c r="B283" s="23" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A284" s="3">
+        <v>14125</v>
+      </c>
+      <c r="B284" s="23" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A285" s="3">
+        <v>14126</v>
+      </c>
+      <c r="B285" s="23" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A286" s="3">
+        <v>14127</v>
+      </c>
+      <c r="B286" s="23" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A287" s="3">
         <v>14128</v>
       </c>
-      <c r="B209" s="24" t="s">
-        <v>481</v>
+      <c r="B287" s="23" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B201">
-    <sortCondition ref="A1:A201"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B287">
+    <sortCondition ref="A1:A287"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9524,6 +11857,959 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74834FCE-95F4-4591-933C-7E036125508A}">
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr defaultColWidth="17.33203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="50.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="110.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="100.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="24" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>654</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FCBD9B-5783-443C-87DE-4B13994EA8C3}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -9561,7 +12847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA087EF-D4CB-4508-81E0-4C5741605FD2}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -9571,13 +12857,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C1" t="s">
         <v>466</v>
-      </c>
-      <c r="B1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -9585,10 +12871,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB870693-8293-4949-A959-8487FA9BCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DBA23C-1608-4CBF-9F45-32C252A0BEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="711">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5816,13 +5816,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>約65周(最速13周)</t>
-  </si>
-  <si>
-    <t>約65周(最速13周)</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>伍窮の億兆龍</t>
   </si>
   <si>
@@ -7040,6 +7033,48 @@
     <rPh sb="5" eb="7">
       <t>トクダイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナ</t>
+  </si>
+  <si>
+    <t>ドット・魔王・ヴァンパイアロード</t>
+  </si>
+  <si>
+    <t>ピクセルスプライツ</t>
+  </si>
+  <si>
+    <t>約8周(※これは交換ではなく、ドット進化に必要なレートを示す。希石の偏りによってレートが増減する。)</t>
+    <rPh sb="0" eb="1">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>約65周(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低13周))</t>
+  </si>
+  <si>
+    <t>約65周(※表示している値は平均をとったもの。獲得するモンスターの種類の偏りによってレートが増減する。(最低13周))</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナの希石(×4),ドットリット(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・魔王・ヴァンパイアロードの希石(×4),ドットリット(×1)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・アテナ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドット・魔王・ヴァンパイアロード</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -8271,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>98</v>
@@ -8345,7 +8380,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>100</v>
@@ -8385,7 +8420,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>101</v>
@@ -8762,7 +8797,7 @@
         <v>211</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>220</v>
@@ -9544,7 +9579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
@@ -9588,7 +9623,7 @@
         <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9596,7 +9631,7 @@
         <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9636,7 +9671,7 @@
         <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9804,7 +9839,7 @@
         <v>916</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9900,7 +9935,7 @@
         <v>1176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9908,7 +9943,7 @@
         <v>1294</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9916,7 +9951,7 @@
         <v>1295</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10428,7 +10463,7 @@
         <v>7757</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10436,7 +10471,7 @@
         <v>7758</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10444,7 +10479,7 @@
         <v>7759</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10452,7 +10487,7 @@
         <v>7760</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10460,7 +10495,7 @@
         <v>7761</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10828,7 +10863,7 @@
         <v>10522</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10860,7 +10895,7 @@
         <v>10531</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10868,7 +10903,7 @@
         <v>10532</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10964,7 +10999,7 @@
         <v>11203</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10980,7 +11015,7 @@
         <v>11216</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11020,7 +11055,7 @@
         <v>11553</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11036,7 +11071,7 @@
         <v>11557</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11052,7 +11087,7 @@
         <v>11560</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11068,7 +11103,7 @@
         <v>11563</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11084,7 +11119,7 @@
         <v>11566</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11108,7 +11143,7 @@
         <v>12112</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11116,7 +11151,7 @@
         <v>12113</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11132,7 +11167,7 @@
         <v>12252</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11156,7 +11191,7 @@
         <v>12260</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11172,7 +11207,7 @@
         <v>12343</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11180,7 +11215,7 @@
         <v>12344</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11204,7 +11239,7 @@
         <v>12685</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11236,7 +11271,7 @@
         <v>12694</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11244,7 +11279,7 @@
         <v>12695</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11268,7 +11303,7 @@
         <v>12857</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11308,7 +11343,7 @@
         <v>12867</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11316,7 +11351,7 @@
         <v>12868</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -11329,527 +11364,543 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="3">
-        <v>13047</v>
+        <v>13045</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>441</v>
+        <v>701</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="3">
-        <v>13048</v>
+        <v>13046</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>442</v>
+        <v>702</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="3">
-        <v>13049</v>
+        <v>13047</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>618</v>
+        <v>441</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="3">
-        <v>13055</v>
+        <v>13048</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>173</v>
+        <v>442</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="3">
-        <v>13056</v>
+        <v>13049</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>174</v>
+        <v>616</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="3">
-        <v>13057</v>
+        <v>13055</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="3">
-        <v>13058</v>
+        <v>13056</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>622</v>
+        <v>174</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="3">
-        <v>13059</v>
+        <v>13057</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>624</v>
+        <v>175</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="3">
-        <v>13060</v>
+        <v>13058</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>176</v>
+        <v>620</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="3">
-        <v>13294</v>
+        <v>13059</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="3">
-        <v>13295</v>
+        <v>13060</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="3">
-        <v>13301</v>
+        <v>13294</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="3">
-        <v>13302</v>
+        <v>13295</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>629</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="3">
-        <v>13303</v>
+        <v>13301</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>457</v>
+        <v>626</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="3">
-        <v>13304</v>
+        <v>13302</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>458</v>
+        <v>627</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="3">
-        <v>13375</v>
+        <v>13303</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>636</v>
+        <v>457</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="3">
-        <v>13381</v>
+        <v>13304</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>189</v>
+        <v>458</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="3">
-        <v>13382</v>
+        <v>13375</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>190</v>
+        <v>634</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="3">
-        <v>13383</v>
+        <v>13381</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="3">
-        <v>13384</v>
+        <v>13382</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="3">
-        <v>13385</v>
+        <v>13383</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>641</v>
+        <v>191</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="3">
-        <v>13494</v>
+        <v>13384</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>646</v>
+        <v>192</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="3">
-        <v>13498</v>
+        <v>13385</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="3">
-        <v>13499</v>
+        <v>13494</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>84</v>
+        <v>644</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="3">
-        <v>13500</v>
+        <v>13498</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>85</v>
+        <v>655</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="3">
-        <v>13501</v>
+        <v>13499</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="3">
-        <v>13502</v>
+        <v>13500</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>650</v>
+        <v>85</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="3">
-        <v>13503</v>
+        <v>13501</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="3">
-        <v>13585</v>
+        <v>13502</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="3">
-        <v>13589</v>
+        <v>13503</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>660</v>
+        <v>87</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="3">
-        <v>13590</v>
+        <v>13585</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>80</v>
+        <v>657</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="3">
-        <v>13591</v>
+        <v>13589</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>81</v>
+        <v>658</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="3">
-        <v>13592</v>
+        <v>13590</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="3">
-        <v>13593</v>
+        <v>13591</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>661</v>
+        <v>81</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="3">
-        <v>13594</v>
+        <v>13592</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="3">
-        <v>13667</v>
+        <v>13593</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>64</v>
+        <v>659</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="3">
-        <v>13794</v>
+        <v>13594</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>668</v>
+        <v>83</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="3">
-        <v>13798</v>
+        <v>13667</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>670</v>
+        <v>64</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="3">
-        <v>13799</v>
+        <v>13794</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>88</v>
+        <v>666</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="3">
-        <v>13800</v>
+        <v>13798</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>89</v>
+        <v>668</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="3">
-        <v>13801</v>
+        <v>13799</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="3">
-        <v>13802</v>
+        <v>13800</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>671</v>
+        <v>89</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="3">
-        <v>13803</v>
+        <v>13801</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="3">
-        <v>13816</v>
+        <v>13802</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="3">
-        <v>13820</v>
+        <v>13803</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>687</v>
+        <v>91</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="3">
-        <v>13821</v>
+        <v>13816</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>76</v>
+        <v>676</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="3">
-        <v>13822</v>
+        <v>13820</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>77</v>
+        <v>685</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="3">
-        <v>13823</v>
+        <v>13821</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="3">
-        <v>13824</v>
+        <v>13822</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>679</v>
+        <v>77</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="3">
-        <v>13825</v>
+        <v>13823</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="3">
-        <v>14018</v>
+        <v>13824</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="3">
-        <v>14022</v>
+        <v>13825</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>689</v>
+        <v>79</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="3">
-        <v>14023</v>
+        <v>14018</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>92</v>
+        <v>686</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="3">
-        <v>14024</v>
+        <v>14022</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>93</v>
+        <v>687</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="3">
-        <v>14025</v>
+        <v>14023</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="3">
-        <v>14026</v>
+        <v>14024</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>690</v>
+        <v>93</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="3">
-        <v>14027</v>
+        <v>14025</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="3">
-        <v>14121</v>
-      </c>
-      <c r="B280" s="23" t="s">
-        <v>472</v>
+        <v>14026</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="3">
-        <v>14122</v>
-      </c>
-      <c r="B281" s="23" t="s">
-        <v>473</v>
+        <v>14027</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="3">
-        <v>14123</v>
+        <v>14121</v>
       </c>
       <c r="B282" s="23" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="3">
-        <v>14124</v>
+        <v>14122</v>
       </c>
       <c r="B283" s="23" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="3">
-        <v>14125</v>
+        <v>14123</v>
       </c>
       <c r="B284" s="23" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="3">
-        <v>14126</v>
+        <v>14124</v>
       </c>
       <c r="B285" s="23" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="3">
-        <v>14127</v>
+        <v>14125</v>
       </c>
       <c r="B286" s="23" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="3">
+        <v>14126</v>
+      </c>
+      <c r="B287" s="23" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A288" s="3">
+        <v>14127</v>
+      </c>
+      <c r="B288" s="23" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A289" s="3">
         <v>14128</v>
       </c>
-      <c r="B287" s="23" t="s">
+      <c r="B289" s="23" t="s">
         <v>479</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B287">
-    <sortCondition ref="A1:A287"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B289">
+    <sortCondition ref="A1:A289"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11858,7 +11909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74834FCE-95F4-4591-933C-7E036125508A}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="17.33203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50.58203125" style="1" customWidth="1"/>
@@ -11876,7 +11927,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>482</v>
@@ -11944,7 +11995,7 @@
         <v>487</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>493</v>
@@ -12074,16 +12125,16 @@
     </row>
     <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>540</v>
+        <v>706</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>489</v>
@@ -12091,16 +12142,16 @@
     </row>
     <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>539</v>
+        <v>705</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>489</v>
@@ -12108,16 +12159,16 @@
     </row>
     <row r="15" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>539</v>
+        <v>705</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>489</v>
@@ -12125,16 +12176,16 @@
     </row>
     <row r="16" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>539</v>
+        <v>705</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>489</v>
@@ -12142,16 +12193,16 @@
     </row>
     <row r="17" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>539</v>
+        <v>705</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>489</v>
@@ -12159,16 +12210,16 @@
     </row>
     <row r="18" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>489</v>
@@ -12176,16 +12227,16 @@
     </row>
     <row r="19" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>489</v>
@@ -12193,16 +12244,16 @@
     </row>
     <row r="20" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>511</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>489</v>
@@ -12210,16 +12261,16 @@
     </row>
     <row r="21" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>489</v>
@@ -12227,16 +12278,16 @@
     </row>
     <row r="22" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>489</v>
@@ -12244,16 +12295,16 @@
     </row>
     <row r="23" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>580</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>489</v>
@@ -12261,7 +12312,7 @@
     </row>
     <row r="24" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>103</v>
@@ -12270,7 +12321,7 @@
         <v>511</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>489</v>
@@ -12278,7 +12329,7 @@
     </row>
     <row r="25" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>103</v>
@@ -12287,7 +12338,7 @@
         <v>510</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>489</v>
@@ -12295,16 +12346,16 @@
     </row>
     <row r="26" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>489</v>
@@ -12312,16 +12363,16 @@
     </row>
     <row r="27" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>489</v>
@@ -12329,16 +12380,16 @@
     </row>
     <row r="28" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>489</v>
@@ -12346,16 +12397,16 @@
     </row>
     <row r="29" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>489</v>
@@ -12363,16 +12414,16 @@
     </row>
     <row r="30" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>489</v>
@@ -12380,16 +12431,16 @@
     </row>
     <row r="31" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>489</v>
@@ -12397,16 +12448,16 @@
     </row>
     <row r="32" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>489</v>
@@ -12414,16 +12465,16 @@
     </row>
     <row r="33" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>489</v>
@@ -12431,7 +12482,7 @@
     </row>
     <row r="34" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>106</v>
@@ -12440,7 +12491,7 @@
         <v>511</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>489</v>
@@ -12448,16 +12499,16 @@
     </row>
     <row r="35" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>489</v>
@@ -12465,16 +12516,16 @@
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>632</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>489</v>
@@ -12482,16 +12533,16 @@
     </row>
     <row r="37" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>489</v>
@@ -12499,16 +12550,16 @@
     </row>
     <row r="38" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>489</v>
@@ -12516,16 +12567,16 @@
     </row>
     <row r="39" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>640</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>489</v>
@@ -12533,16 +12584,16 @@
     </row>
     <row r="40" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>489</v>
@@ -12550,16 +12601,16 @@
     </row>
     <row r="41" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>651</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>489</v>
@@ -12567,16 +12618,16 @@
     </row>
     <row r="42" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>489</v>
@@ -12584,16 +12635,16 @@
     </row>
     <row r="43" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>489</v>
@@ -12601,16 +12652,16 @@
     </row>
     <row r="44" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>489</v>
@@ -12618,16 +12669,16 @@
     </row>
     <row r="45" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>489</v>
@@ -12635,16 +12686,16 @@
     </row>
     <row r="46" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>489</v>
@@ -12652,16 +12703,16 @@
     </row>
     <row r="47" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>489</v>
@@ -12669,16 +12720,16 @@
     </row>
     <row r="48" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>489</v>
@@ -12686,16 +12737,16 @@
     </row>
     <row r="49" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>489</v>
@@ -12703,16 +12754,16 @@
     </row>
     <row r="50" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>489</v>
@@ -12720,16 +12771,16 @@
     </row>
     <row r="51" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>489</v>
@@ -12737,16 +12788,16 @@
     </row>
     <row r="52" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>489</v>
@@ -12754,16 +12805,16 @@
     </row>
     <row r="53" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>489</v>
@@ -12771,16 +12822,16 @@
     </row>
     <row r="54" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>489</v>
@@ -12788,18 +12839,52 @@
     </row>
     <row r="55" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>489</v>
       </c>
     </row>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DBA23C-1608-4CBF-9F45-32C252A0BEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC880AC2-1099-42CE-9460-D69EF691F09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="787">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -4512,20 +4512,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>10"万"</t>
-    <rPh sb="3" eb="4">
-      <t>マン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>11"万"</t>
-    <rPh sb="3" eb="4">
-      <t>マン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>39～45</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -7075,6 +7061,342 @@
   </si>
   <si>
     <t>ドット・魔王・ヴァンパイアロード</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>背景モンスター</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>14018_1</t>
+  </si>
+  <si>
+    <t>14018_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13816_1</t>
+  </si>
+  <si>
+    <t>13816_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13794_1</t>
+  </si>
+  <si>
+    <t>13794_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>全体ver</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13585_1</t>
+  </si>
+  <si>
+    <t>13585_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13494_1</t>
+  </si>
+  <si>
+    <t>13494_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13375_1</t>
+  </si>
+  <si>
+    <t>13375_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13049_1</t>
+  </si>
+  <si>
+    <t>13049_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>12857_1</t>
+  </si>
+  <si>
+    <t>12857_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>12685_1</t>
+  </si>
+  <si>
+    <t>12685_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10522_1</t>
+  </si>
+  <si>
+    <t>10522_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>12252_1</t>
+  </si>
+  <si>
+    <t>12252_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11553_1</t>
+  </si>
+  <si>
+    <t>11553_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11548_1</t>
+  </si>
+  <si>
+    <t>11548_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11203_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11203_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11192_1</t>
+  </si>
+  <si>
+    <t>11192_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11115_1</t>
+  </si>
+  <si>
+    <t>11115_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>8914_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>8914_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>8915_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>8915_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9227_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9228_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9227_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9228_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9455_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9456_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9716_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9718_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9870_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>億兆龍・アグリゲート</t>
+    <rPh sb="0" eb="3">
+      <t>オクチョウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9872_1</t>
+  </si>
+  <si>
+    <t>9872_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9455_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9456_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9716_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9718_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9870_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>9872_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10297_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極悪生命体・ゴクレグス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10298_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10297_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10198_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>神魔の裁断者・メタトロン</t>
+    <rPh sb="0" eb="1">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイダン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>3535_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>3535_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>銀翼の白迅帝・デイトナ</t>
+    <rPh sb="0" eb="2">
+      <t>ギンヨク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7851_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7851_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13045_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>13045_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天境の白霹竜・ノヴァ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10301_1</t>
+  </si>
+  <si>
+    <t>10301_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>冥境の黒熾龍・ゴウテン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10304_1</t>
+  </si>
+  <si>
+    <t>10304_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>轟爆の鳳凰帝・グリームフェニックス</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウバク</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ホウオウテイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>14131_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>14131_1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -7086,7 +7408,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7269,6 +7591,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="34">
@@ -7752,7 +8080,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7831,6 +8159,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -8207,21 +8538,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="156.4140625" style="15" customWidth="1"/>
     <col min="4" max="8" width="25.58203125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="163.75" style="14" customWidth="1"/>
-    <col min="10" max="10" width="71.1640625" style="14" customWidth="1"/>
-    <col min="11" max="11" width="71.08203125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="255.5" style="14" customWidth="1"/>
-    <col min="13" max="13" width="151.1640625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="104.1640625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="50.58203125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="163.75" style="14" customWidth="1"/>
+    <col min="11" max="11" width="71.1640625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="71.08203125" style="14" customWidth="1"/>
+    <col min="13" max="13" width="255.5" style="14" customWidth="1"/>
+    <col min="14" max="14" width="151.1640625" style="14" customWidth="1"/>
+    <col min="15" max="15" width="104.1640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8246,26 +8578,29 @@
       <c r="H1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
@@ -8288,25 +8623,28 @@
         <v>28</v>
       </c>
       <c r="H2" s="10"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12"/>
+      <c r="L2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="12"/>
       <c r="N2" s="12"/>
-    </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>98</v>
@@ -8324,22 +8662,25 @@
         <v>28</v>
       </c>
       <c r="H3" s="10"/>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="12"/>
       <c r="N3" s="12"/>
-    </row>
-    <row r="4" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
@@ -8362,25 +8703,28 @@
         <v>28</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="L4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
-    </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>100</v>
@@ -8398,29 +8742,32 @@
         <v>28</v>
       </c>
       <c r="H5" s="10"/>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="L5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="12"/>
+      <c r="O5" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>101</v>
@@ -8440,24 +8787,27 @@
       <c r="H6" s="10">
         <v>30</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="L6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="12"/>
+      <c r="O6" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="22" t="s">
         <v>102</v>
       </c>
@@ -8478,24 +8828,27 @@
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="22" t="s">
         <v>102</v>
       </c>
@@ -8516,24 +8869,27 @@
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="M8" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="N8" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="22" t="s">
         <v>102</v>
       </c>
@@ -8554,22 +8910,25 @@
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M9" s="12"/>
       <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O9" s="12"/>
+    </row>
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="22" t="s">
         <v>102</v>
       </c>
@@ -8590,24 +8949,27 @@
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="L10" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="M10" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="N10" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O10" s="12"/>
+    </row>
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="22" t="s">
         <v>102</v>
       </c>
@@ -8628,26 +8990,29 @@
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="N11" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="22" t="s">
         <v>206</v>
       </c>
@@ -8670,20 +9035,23 @@
         <v>220</v>
       </c>
       <c r="H12" s="9"/>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="12"/>
+      <c r="M12" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="M12" s="12"/>
       <c r="N12" s="12"/>
-    </row>
-    <row r="13" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O12" s="12"/>
+    </row>
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="22" t="s">
         <v>206</v>
       </c>
@@ -8704,20 +9072,23 @@
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="M13" s="12"/>
       <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O13" s="12"/>
+    </row>
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="22" t="s">
         <v>206</v>
       </c>
@@ -8740,20 +9111,23 @@
         <v>220</v>
       </c>
       <c r="H14" s="9"/>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12"/>
+      <c r="M14" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
@@ -8776,20 +9150,23 @@
         <v>220</v>
       </c>
       <c r="H15" s="9"/>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="12"/>
+      <c r="M15" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="M15" s="12"/>
       <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="22" t="s">
         <v>206</v>
       </c>
@@ -8797,7 +9174,7 @@
         <v>211</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>220</v>
@@ -8812,24 +9189,27 @@
         <v>220</v>
       </c>
       <c r="H16" s="9"/>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="M16" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="12"/>
+      <c r="O16" s="11" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="22" t="s">
         <v>206</v>
       </c>
@@ -8852,24 +9232,27 @@
         <v>220</v>
       </c>
       <c r="H17" s="9"/>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12"/>
+      <c r="M17" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="M17" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="N17" s="21" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="N17" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="O17" s="21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="22" t="s">
         <v>289</v>
       </c>
@@ -8888,20 +9271,23 @@
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="12"/>
+      <c r="M18" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="M18" s="12"/>
       <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O18" s="12"/>
+    </row>
+    <row r="19" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="22" t="s">
         <v>289</v>
       </c>
@@ -8918,20 +9304,23 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="12"/>
+      <c r="M19" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="M19" s="12"/>
       <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O19" s="12"/>
+    </row>
+    <row r="20" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="22" t="s">
         <v>289</v>
       </c>
@@ -8948,20 +9337,23 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="12"/>
+      <c r="M20" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="M20" s="12"/>
       <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O20" s="12"/>
+    </row>
+    <row r="21" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="22" t="s">
         <v>289</v>
       </c>
@@ -8980,20 +9372,23 @@
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="12"/>
+      <c r="M21" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="M21" s="12"/>
       <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="22" t="s">
         <v>289</v>
       </c>
@@ -9001,7 +9396,7 @@
         <v>302</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>303</v>
@@ -9014,18 +9409,21 @@
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="J22" s="12"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="12"/>
+      <c r="M22" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="M22" s="12"/>
       <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O22" s="12"/>
+    </row>
+    <row r="23" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="22" t="s">
         <v>289</v>
       </c>
@@ -9033,7 +9431,7 @@
         <v>305</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>306</v>
@@ -9046,20 +9444,23 @@
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="J23" s="12"/>
       <c r="K23" s="12"/>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="12"/>
+      <c r="M23" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="N23" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O23" s="12"/>
+    </row>
+    <row r="24" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="22" t="s">
         <v>289</v>
       </c>
@@ -9078,18 +9479,21 @@
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="J24" s="12"/>
+      <c r="I24" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>423</v>
+      </c>
       <c r="K24" s="12"/>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="12"/>
+      <c r="M24" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="M24" s="12"/>
       <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O24" s="12"/>
+    </row>
+    <row r="25" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="22" t="s">
         <v>289</v>
       </c>
@@ -9108,20 +9512,23 @@
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="11" t="s">
-        <v>426</v>
+      <c r="I25" s="9" t="s">
+        <v>750</v>
       </c>
       <c r="J25" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="K25" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="12"/>
+      <c r="M25" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="M25" s="12"/>
       <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O25" s="12"/>
+    </row>
+    <row r="26" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="22" t="s">
         <v>289</v>
       </c>
@@ -9140,20 +9547,23 @@
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="11" t="s">
-        <v>427</v>
+      <c r="I26" s="9" t="s">
+        <v>760</v>
       </c>
       <c r="J26" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="K26" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="12"/>
+      <c r="M26" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="M26" s="12"/>
       <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O26" s="12"/>
+    </row>
+    <row r="27" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="22" t="s">
         <v>289</v>
       </c>
@@ -9172,20 +9582,23 @@
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="12"/>
+      <c r="M27" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="M27" s="12"/>
       <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O27" s="12"/>
+    </row>
+    <row r="28" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="22" t="s">
         <v>289</v>
       </c>
@@ -9193,7 +9606,7 @@
         <v>316</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>317</v>
@@ -9208,18 +9621,21 @@
         <v>306</v>
       </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="J28" s="12"/>
       <c r="K28" s="12"/>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="12"/>
+      <c r="M28" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="M28" s="12"/>
       <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O28" s="12"/>
+    </row>
+    <row r="29" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="22" t="s">
         <v>289</v>
       </c>
@@ -9227,7 +9643,7 @@
         <v>319</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>320</v>
@@ -9242,20 +9658,23 @@
         <v>321</v>
       </c>
       <c r="H29" s="9"/>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="J29" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="J29" s="12"/>
       <c r="K29" s="12"/>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="12"/>
+      <c r="M29" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="N29" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O29" s="12"/>
+    </row>
+    <row r="30" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="22" t="s">
         <v>394</v>
       </c>
@@ -9263,7 +9682,7 @@
         <v>395</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>402</v>
@@ -9276,22 +9695,25 @@
         <v>306</v>
       </c>
       <c r="H30" s="9"/>
-      <c r="I30" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="J30" s="12"/>
-      <c r="K30" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="11" t="s">
-        <v>428</v>
-      </c>
+      <c r="I30" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="K30" s="12"/>
+      <c r="L30" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="M30" s="12"/>
       <c r="N30" s="11" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>426</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="22" t="s">
         <v>394</v>
       </c>
@@ -9299,7 +9721,7 @@
         <v>396</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>306</v>
@@ -9308,28 +9730,29 @@
         <v>292</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="9" t="s">
-        <v>405</v>
-      </c>
+      <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="L31" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="N31" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="L31" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O31" s="12"/>
+    </row>
+    <row r="32" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="22" t="s">
         <v>394</v>
       </c>
@@ -9344,26 +9767,27 @@
         <v>404</v>
       </c>
       <c r="F32" s="9"/>
-      <c r="G32" s="9" t="s">
-        <v>406</v>
-      </c>
+      <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I32" s="12"/>
+        <v>405</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>772</v>
+      </c>
       <c r="J32" s="12"/>
-      <c r="K32" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="L32" s="12"/>
-      <c r="M32" s="11" t="s">
-        <v>435</v>
-      </c>
+      <c r="K32" s="12"/>
+      <c r="L32" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="M32" s="12"/>
       <c r="N32" s="11" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>433</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="22" t="s">
         <v>394</v>
       </c>
@@ -9371,35 +9795,38 @@
         <v>398</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>408</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>410</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9">
         <v>30</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="K33" s="12"/>
+      <c r="L33" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="M33" s="12"/>
+      <c r="N33" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="J33" s="12"/>
-      <c r="K33" s="11" t="s">
-        <v>437</v>
-      </c>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11" t="s">
+      <c r="O33" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="N33" s="11" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="34" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="22" t="s">
         <v>394</v>
       </c>
@@ -9407,7 +9834,7 @@
         <v>399</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>306</v>
@@ -9418,20 +9845,23 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="K34" s="12"/>
+      <c r="L34" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="J34" s="12"/>
-      <c r="K34" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="L34" s="12"/>
       <c r="M34" s="12"/>
-      <c r="N34" s="11" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="N34" s="12"/>
+      <c r="O34" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="22" t="s">
         <v>394</v>
       </c>
@@ -9439,33 +9869,36 @@
         <v>400</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>415</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>417</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>447</v>
-      </c>
-      <c r="J35" s="12"/>
+        <v>405</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>445</v>
+      </c>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
-      <c r="M35" s="11" t="s">
-        <v>453</v>
-      </c>
+      <c r="M35" s="12"/>
       <c r="N35" s="11" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>451</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="22" t="s">
         <v>394</v>
       </c>
@@ -9473,77 +9906,83 @@
         <v>401</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>418</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>420</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9">
         <v>30</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="K36" s="12"/>
+      <c r="L36" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="M36" s="12"/>
+      <c r="N36" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="L36" s="12"/>
-      <c r="M36" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="N36" s="11" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O36" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9">
         <v>30</v>
       </c>
-      <c r="I37" s="12"/>
+      <c r="I37" s="9" t="s">
+        <v>786</v>
+      </c>
       <c r="J37" s="12"/>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="12"/>
+      <c r="L37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="M37" s="12"/>
-      <c r="N37" s="11" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="M37" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="N37" s="12"/>
+      <c r="O37" s="11" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="39" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="40" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="41" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="42" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="44" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="45" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="46" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="47" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="48" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="49" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="50" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="51" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -9579,22 +10018,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:C296"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="43.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1" s="1" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3">
         <v>112</v>
       </c>
@@ -9602,7 +10045,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3">
         <v>114</v>
       </c>
@@ -9610,7 +10053,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3">
         <v>116</v>
       </c>
@@ -9618,63 +10061,63 @@
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3">
         <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
         <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
         <v>152</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
         <v>153</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
         <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
         <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
         <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
         <v>322</v>
       </c>
@@ -9682,7 +10125,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
         <v>323</v>
       </c>
@@ -9690,7 +10133,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
         <v>324</v>
       </c>
@@ -9698,7 +10141,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
         <v>325</v>
       </c>
@@ -9706,7 +10149,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
         <v>326</v>
       </c>
@@ -9839,7 +10282,7 @@
         <v>916</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9871,7 +10314,7 @@
         <v>1085</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9879,7 +10322,7 @@
         <v>1086</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9887,7 +10330,7 @@
         <v>1087</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9935,7 +10378,7 @@
         <v>1176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9943,7 +10386,7 @@
         <v>1294</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9951,7 +10394,7 @@
         <v>1295</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9959,7 +10402,7 @@
         <v>1325</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9967,7 +10410,7 @@
         <v>1326</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9975,7 +10418,7 @@
         <v>1327</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9983,7 +10426,7 @@
         <v>1328</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -9991,7 +10434,7 @@
         <v>1329</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -10098,7 +10541,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3">
         <v>3320</v>
       </c>
@@ -10106,7 +10549,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3">
         <v>3321</v>
       </c>
@@ -10114,7 +10557,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3">
         <v>3322</v>
       </c>
@@ -10122,7 +10565,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3">
         <v>3323</v>
       </c>
@@ -10130,7 +10573,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3">
         <v>3324</v>
       </c>
@@ -10138,7 +10581,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3">
         <v>3325</v>
       </c>
@@ -10146,1761 +10589,1919 @@
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3">
+        <v>3535</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3">
         <v>3700</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3">
         <v>3701</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3">
         <v>3702</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3">
         <v>3795</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="3">
         <v>3826</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="3">
+      <c r="B76" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="3">
         <v>3827</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="3">
         <v>3891</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3">
         <v>3911</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="3">
         <v>3971</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="3">
-        <v>3973</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3">
-        <v>4014</v>
+        <v>3974</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3">
-        <v>4369</v>
+        <v>4014</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3">
-        <v>4370</v>
+        <v>4369</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3">
-        <v>4371</v>
+        <v>4370</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3">
-        <v>4372</v>
+        <v>4371</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3">
-        <v>4373</v>
+        <v>4372</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3">
-        <v>5739</v>
+        <v>4373</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3">
-        <v>6073</v>
+        <v>5739</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3">
-        <v>6074</v>
+        <v>6073</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3">
-        <v>6178</v>
+        <v>6077</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>249</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3">
-        <v>6522</v>
+        <v>6178</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3">
-        <v>6607</v>
+        <v>6522</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3">
-        <v>6608</v>
+        <v>6607</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3">
-        <v>6609</v>
+        <v>6608</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3">
-        <v>6878</v>
+        <v>6609</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3">
-        <v>7020</v>
+        <v>6878</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3">
-        <v>7022</v>
+        <v>7021</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="3">
-        <v>7023</v>
+        <v>7022</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3">
-        <v>7042</v>
+        <v>7023</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3">
-        <v>7493</v>
+        <v>7042</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>252</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3">
-        <v>7680</v>
+        <v>7493</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3">
-        <v>7681</v>
+        <v>7680</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3">
-        <v>7684</v>
+        <v>7681</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3">
-        <v>7686</v>
+        <v>7684</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3">
-        <v>7757</v>
+        <v>7686</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>696</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3">
-        <v>7758</v>
+        <v>7757</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3">
+        <v>7758</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="3">
         <v>7759</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B113" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="3">
+        <v>7760</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="3">
+        <v>7761</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="3">
-        <v>7760</v>
-      </c>
-      <c r="B113" s="3" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="3">
+        <v>7851</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="3">
+        <v>8298</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="3">
+        <v>8551</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="3">
+        <v>8552</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="3">
+        <v>8553</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="3">
+        <v>8554</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="3">
+        <v>8555</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="3">
+        <v>8728</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="3">
+        <v>8914</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="3">
+        <v>8915</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="3">
+        <v>8916</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="3">
+        <v>9000</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="3">
+        <v>9227</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="3">
+        <v>9228</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="3">
+        <v>9229</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="3">
+        <v>9454</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="3">
+        <v>9455</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="3">
+        <v>9456</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="3">
+        <v>9457</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" s="3">
+        <v>9534</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="3">
+        <v>9716</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="3">
+        <v>9718</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" s="3">
+        <v>9827</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" s="3">
+        <v>9870</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" s="3">
+        <v>9872</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" s="3">
+        <v>10007</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" s="3">
+        <v>10008</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" s="3">
+        <v>10009</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" s="3">
+        <v>10010</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="3">
+        <v>10011</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" s="3">
+        <v>10022</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" s="3">
+        <v>10023</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" s="3">
+        <v>10024</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" s="3">
+        <v>10025</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" s="3">
+        <v>10026</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" s="3">
+        <v>10114</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" s="3">
+        <v>10297</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" s="3">
+        <v>10298</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>766</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" s="3">
+        <v>10301</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>778</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" s="3">
+        <v>10304</v>
+      </c>
+      <c r="B155" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" s="3">
+        <v>10512</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="3">
+        <v>10513</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="3">
+        <v>10514</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="3">
+        <v>10515</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="3">
+        <v>10516</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" s="3">
+        <v>10517</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" s="3">
+        <v>10518</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" s="3">
+        <v>10519</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="3">
+        <v>10520</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" s="3">
+        <v>10521</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" s="3">
+        <v>10522</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" s="3">
+        <v>10528</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" s="3">
+        <v>10529</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" s="3">
+        <v>10530</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" s="3">
+        <v>10531</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" s="3">
+        <v>10532</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" s="3">
+        <v>10533</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" s="3">
+        <v>11037</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" s="3">
+        <v>11038</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" s="3">
+        <v>11039</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" s="3">
+        <v>11040</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" s="3">
+        <v>11046</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" s="3">
+        <v>11108</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" s="3">
+        <v>11115</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" s="3">
+        <v>11119</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" s="3">
+        <v>11192</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" s="3">
+        <v>11196</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" s="3">
+        <v>11203</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" s="3">
+        <v>11207</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" s="3">
+        <v>11216</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" s="3">
+        <v>11217</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A187" s="3">
+        <v>11218</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A188" s="3">
+        <v>11548</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A189" s="3">
+        <v>11552</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A190" s="3">
+        <v>11553</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A191" s="3">
+        <v>11556</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" s="3">
+        <v>11557</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A193" s="3">
+        <v>11559</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A194" s="3">
+        <v>11560</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A195" s="3">
+        <v>11562</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A196" s="3">
+        <v>11563</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A197" s="3">
+        <v>11565</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A198" s="3">
+        <v>11566</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A199" s="3">
+        <v>11568</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A200" s="3">
+        <v>11588</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A201" s="3">
+        <v>12112</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A202" s="3">
+        <v>12113</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A203" s="3">
+        <v>12114</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A204" s="3">
+        <v>12252</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A205" s="3">
+        <v>12257</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A206" s="3">
+        <v>12258</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A207" s="3">
+        <v>12260</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A208" s="3">
+        <v>12261</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A209" s="3">
+        <v>12343</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A210" s="3">
+        <v>12344</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A211" s="3">
+        <v>12345</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A212" s="3">
+        <v>12346</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A213" s="3">
+        <v>12685</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A214" s="3">
+        <v>12691</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A215" s="3">
+        <v>12692</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A216" s="3">
+        <v>12693</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A217" s="3">
+        <v>12694</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A218" s="3">
+        <v>12695</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" s="3">
+        <v>12696</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A220" s="3">
+        <v>12697</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A221" s="3">
+        <v>12857</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A222" s="3">
+        <v>12863</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A223" s="3">
+        <v>12864</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A224" s="3">
+        <v>12865</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A225" s="3">
+        <v>12866</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A226" s="3">
+        <v>12867</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A227" s="3">
+        <v>12868</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A228" s="3">
+        <v>12869</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A229" s="3">
+        <v>13045</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="3">
-        <v>7761</v>
-      </c>
-      <c r="B114" s="3" t="s">
+      <c r="C229" s="3" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A230" s="3">
+        <v>13046</v>
+      </c>
+      <c r="B230" s="3" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="3">
-        <v>8298</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="3">
-        <v>8551</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="3">
-        <v>8552</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="3">
-        <v>8553</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="3">
-        <v>8554</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="3">
-        <v>8555</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="3">
-        <v>8728</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="3">
-        <v>8914</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="3">
-        <v>8915</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="3">
-        <v>8916</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" s="3">
-        <v>9000</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="3">
-        <v>9227</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="3">
-        <v>9228</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="3">
-        <v>9229</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="3">
-        <v>9454</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" s="3">
-        <v>9455</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" s="3">
-        <v>9456</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" s="3">
-        <v>9457</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" s="3">
-        <v>9534</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" s="3">
-        <v>9716</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135" s="3">
-        <v>9718</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" s="3">
-        <v>9827</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" s="3">
-        <v>9870</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138" s="3">
-        <v>10007</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139" s="3">
-        <v>10008</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140" s="3">
-        <v>10009</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141" s="3">
-        <v>10010</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142" s="3">
-        <v>10011</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" s="3">
-        <v>10022</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" s="3">
-        <v>10023</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="3">
-        <v>10024</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146" s="3">
-        <v>10025</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147" s="3">
-        <v>10026</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A148" s="3">
-        <v>10114</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A149" s="3">
-        <v>10297</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A150" s="3">
-        <v>10512</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A151" s="3">
-        <v>10513</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152" s="3">
-        <v>10514</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153" s="3">
-        <v>10515</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A154" s="3">
-        <v>10516</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A155" s="3">
-        <v>10517</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156" s="3">
-        <v>10518</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A157" s="3">
-        <v>10519</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158" s="3">
-        <v>10520</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A159" s="3">
-        <v>10521</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160" s="3">
-        <v>10522</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161" s="3">
-        <v>10528</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162" s="3">
-        <v>10529</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163" s="3">
-        <v>10530</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164" s="3">
-        <v>10531</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165" s="3">
-        <v>10532</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" s="3">
-        <v>10533</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167" s="3">
-        <v>11037</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168" s="3">
-        <v>11038</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169" s="3">
-        <v>11039</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170" s="3">
-        <v>11040</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171" s="3">
-        <v>11046</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172" s="3">
-        <v>11108</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173" s="3">
-        <v>11115</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A174" s="3">
-        <v>11119</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A175" s="3">
-        <v>11192</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A176" s="3">
-        <v>11196</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177" s="3">
-        <v>11203</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A178" s="3">
-        <v>11207</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179" s="3">
-        <v>11216</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180" s="3">
-        <v>11217</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A181" s="3">
-        <v>11218</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182" s="3">
-        <v>11548</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183" s="3">
-        <v>11552</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184" s="3">
-        <v>11553</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" s="3">
-        <v>11556</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186" s="3">
-        <v>11557</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187" s="3">
-        <v>11559</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188" s="3">
-        <v>11560</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A189" s="3">
-        <v>11562</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190" s="3">
-        <v>11563</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191" s="3">
-        <v>11565</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192" s="3">
-        <v>11566</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A193" s="3">
-        <v>11568</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A194" s="3">
-        <v>11588</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A195" s="3">
-        <v>12112</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A196" s="3">
-        <v>12113</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A197" s="3">
-        <v>12114</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A198" s="3">
-        <v>12252</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A199" s="3">
-        <v>12257</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A200" s="3">
-        <v>12258</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A201" s="3">
-        <v>12260</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A202" s="3">
-        <v>12261</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A203" s="3">
-        <v>12343</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A204" s="3">
-        <v>12344</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A205" s="3">
-        <v>12345</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A206" s="3">
-        <v>12346</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A207" s="3">
-        <v>12685</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A208" s="3">
-        <v>12691</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A209" s="3">
-        <v>12692</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A210" s="3">
-        <v>12693</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A211" s="3">
-        <v>12694</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A212" s="3">
-        <v>12695</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A213" s="3">
-        <v>12696</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A214" s="3">
-        <v>12697</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A215" s="3">
-        <v>12857</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A216" s="3">
-        <v>12863</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A217" s="3">
-        <v>12864</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A218" s="3">
-        <v>12865</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A219" s="3">
-        <v>12866</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A220" s="3">
-        <v>12867</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A221" s="3">
-        <v>12868</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A222" s="3">
-        <v>12869</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A223" s="3">
-        <v>13045</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A224" s="3">
-        <v>13046</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A225" s="3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A231" s="3">
         <v>13047</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A226" s="3">
+      <c r="B231" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A232" s="3">
         <v>13048</v>
       </c>
-      <c r="B226" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A227" s="3">
+      <c r="B232" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A233" s="3">
         <v>13049</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A228" s="3">
+      <c r="B233" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A234" s="3">
         <v>13055</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B234" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A229" s="3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A235" s="3">
         <v>13056</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B235" s="3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A230" s="3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A236" s="3">
         <v>13057</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B236" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A231" s="3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A237" s="3">
         <v>13058</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B237" s="3" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A238" s="3">
+        <v>13059</v>
+      </c>
+      <c r="B238" s="3" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A232" s="3">
-        <v>13059</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A233" s="3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A239" s="3">
         <v>13060</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B239" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A234" s="3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A240" s="3">
         <v>13294</v>
       </c>
-      <c r="B234" s="3" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A235" s="3">
+      <c r="B240" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A241" s="3">
         <v>13295</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B241" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A236" s="3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A242" s="3">
         <v>13301</v>
       </c>
-      <c r="B236" s="3" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A237" s="3">
+      <c r="B242" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A243" s="3">
         <v>13302</v>
       </c>
-      <c r="B237" s="3" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A238" s="3">
+      <c r="B243" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A244" s="3">
         <v>13303</v>
       </c>
-      <c r="B238" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A239" s="3">
+      <c r="B244" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A245" s="3">
         <v>13304</v>
       </c>
-      <c r="B239" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A240" s="3">
+      <c r="B245" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A246" s="3">
         <v>13375</v>
       </c>
-      <c r="B240" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A241" s="3">
+      <c r="B246" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A247" s="3">
         <v>13381</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B247" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A242" s="3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A248" s="3">
         <v>13382</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B248" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A243" s="3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A249" s="3">
         <v>13383</v>
       </c>
-      <c r="B243" s="3" t="s">
+      <c r="B249" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A244" s="3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A250" s="3">
         <v>13384</v>
       </c>
-      <c r="B244" s="3" t="s">
+      <c r="B250" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A245" s="3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A251" s="3">
         <v>13385</v>
       </c>
-      <c r="B245" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A246" s="3">
+      <c r="B251" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A252" s="3">
         <v>13494</v>
       </c>
-      <c r="B246" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A247" s="3">
+      <c r="B252" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A253" s="3">
         <v>13498</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B253" s="3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A254" s="3">
+        <v>13499</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A255" s="3">
+        <v>13500</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A256" s="3">
+        <v>13501</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A257" s="3">
+        <v>13502</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A258" s="3">
+        <v>13503</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A259" s="3">
+        <v>13585</v>
+      </c>
+      <c r="B259" s="3" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A248" s="3">
-        <v>13499</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A249" s="3">
-        <v>13500</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A250" s="3">
-        <v>13501</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A251" s="3">
-        <v>13502</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A252" s="3">
-        <v>13503</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A253" s="3">
-        <v>13585</v>
-      </c>
-      <c r="B253" s="3" t="s">
+      <c r="C259" s="3" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A260" s="3">
+        <v>13589</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A261" s="3">
+        <v>13590</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A262" s="3">
+        <v>13591</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A263" s="3">
+        <v>13592</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A264" s="3">
+        <v>13593</v>
+      </c>
+      <c r="B264" s="3" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A254" s="3">
-        <v>13589</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A255" s="3">
-        <v>13590</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A256" s="3">
-        <v>13591</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A257" s="3">
-        <v>13592</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A258" s="3">
-        <v>13593</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A259" s="3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A265" s="3">
         <v>13594</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B265" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A260" s="3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A266" s="3">
         <v>13667</v>
       </c>
-      <c r="B260" s="3" t="s">
+      <c r="B266" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A261" s="3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A267" s="3">
         <v>13794</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="B267" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A268" s="3">
+        <v>13798</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A262" s="3">
-        <v>13798</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A263" s="3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A269" s="3">
         <v>13799</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B269" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A264" s="3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A270" s="3">
         <v>13800</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B270" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A265" s="3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A271" s="3">
         <v>13801</v>
       </c>
-      <c r="B265" s="3" t="s">
+      <c r="B271" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A266" s="3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A272" s="3">
         <v>13802</v>
       </c>
-      <c r="B266" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A267" s="3">
+      <c r="B272" s="3" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A273" s="3">
         <v>13803</v>
       </c>
-      <c r="B267" s="3" t="s">
+      <c r="B273" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A268" s="3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A274" s="3">
         <v>13816</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A269" s="3">
+      <c r="B274" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A275" s="3">
         <v>13820</v>
       </c>
-      <c r="B269" s="3" t="s">
+      <c r="B275" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A276" s="3">
+        <v>13821</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A277" s="3">
+        <v>13822</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A278" s="3">
+        <v>13823</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A279" s="3">
+        <v>13824</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A280" s="3">
+        <v>13825</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A281" s="3">
+        <v>14018</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A282" s="3">
+        <v>14022</v>
+      </c>
+      <c r="B282" s="3" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A270" s="3">
-        <v>13821</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A271" s="3">
-        <v>13822</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A272" s="3">
-        <v>13823</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A273" s="3">
-        <v>13824</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A274" s="3">
-        <v>13825</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A275" s="3">
-        <v>14018</v>
-      </c>
-      <c r="B275" s="3" t="s">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A283" s="3">
+        <v>14023</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A284" s="3">
+        <v>14024</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A285" s="3">
+        <v>14025</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A286" s="3">
+        <v>14026</v>
+      </c>
+      <c r="B286" s="3" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A276" s="3">
-        <v>14022</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A277" s="3">
-        <v>14023</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A278" s="3">
-        <v>14024</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A279" s="3">
-        <v>14025</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A280" s="3">
-        <v>14026</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A281" s="3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A287" s="3">
         <v>14027</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="B287" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A282" s="3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A288" s="3">
         <v>14121</v>
       </c>
-      <c r="B282" s="23" t="s">
+      <c r="B288" s="23" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A289" s="3">
+        <v>14122</v>
+      </c>
+      <c r="B289" s="23" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A290" s="3">
+        <v>14123</v>
+      </c>
+      <c r="B290" s="23" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A283" s="3">
-        <v>14122</v>
-      </c>
-      <c r="B283" s="23" t="s">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A291" s="3">
+        <v>14124</v>
+      </c>
+      <c r="B291" s="23" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A284" s="3">
-        <v>14123</v>
-      </c>
-      <c r="B284" s="23" t="s">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A292" s="3">
+        <v>14125</v>
+      </c>
+      <c r="B292" s="23" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A285" s="3">
-        <v>14124</v>
-      </c>
-      <c r="B285" s="23" t="s">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A293" s="3">
+        <v>14126</v>
+      </c>
+      <c r="B293" s="23" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A286" s="3">
-        <v>14125</v>
-      </c>
-      <c r="B286" s="23" t="s">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A294" s="3">
+        <v>14127</v>
+      </c>
+      <c r="B294" s="23" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A287" s="3">
-        <v>14126</v>
-      </c>
-      <c r="B287" s="23" t="s">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A295" s="3">
+        <v>14128</v>
+      </c>
+      <c r="B295" s="23" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A288" s="3">
-        <v>14127</v>
-      </c>
-      <c r="B288" s="23" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A289" s="3">
-        <v>14128</v>
-      </c>
-      <c r="B289" s="23" t="s">
-        <v>479</v>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A296" s="3">
+        <v>14131</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B289">
-    <sortCondition ref="A1:A289"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B295">
+    <sortCondition ref="A1:A295"/>
   </sortState>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11921,971 +12522,971 @@
   <sheetData>
     <row r="1" spans="1:5" s="24" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>533</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -12942,13 +13543,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1" t="s">
         <v>464</v>
-      </c>
-      <c r="B1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -12956,10 +13557,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC880AC2-1099-42CE-9460-D69EF691F09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E949EAD-BDA6-49C3-B5EA-247D90FB3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="4130" yWindow="1450" windowWidth="14400" windowHeight="8170" activeTab="4" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="786">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -5133,13 +5133,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>未定</t>
-    <rPh sb="0" eb="2">
-      <t>ミテイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>※1極キング系について、ルビードラ・サファイアドラ・エメラルドドラは各2体確定。ゴールドドラ・メタルドラは1Fと6Fで出現した属性のものが計2体ドロップします。 ※2記載数は最大値です。乱入階層により一部ドロップが減少します。
 （3F：属性軽減たまドラ -1体、6F：極キング系 -4体、9F：宝玉などのランダム枠 -1体）※3属性軽減たまドラは元が不確定のため0体になる場合もあります。</t>
     <phoneticPr fontId="18"/>
@@ -7408,7 +7401,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8539,7 +8532,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="156.4140625" style="15" customWidth="1"/>
@@ -8553,7 +8546,7 @@
     <col min="15" max="15" width="104.1640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8579,7 +8572,7 @@
         <v>36</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>268</v>
@@ -8600,7 +8593,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
@@ -8624,7 +8617,7 @@
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>5</v>
@@ -8639,12 +8632,12 @@
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
     </row>
-    <row r="3" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>98</v>
@@ -8663,7 +8656,7 @@
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>14</v>
@@ -8680,7 +8673,7 @@
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
     </row>
-    <row r="4" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
@@ -8704,7 +8697,7 @@
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>25</v>
@@ -8719,12 +8712,12 @@
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
     </row>
-    <row r="5" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>100</v>
@@ -8743,7 +8736,7 @@
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>19</v>
@@ -8762,12 +8755,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>101</v>
@@ -8788,7 +8781,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>21</v>
@@ -8807,7 +8800,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A7" s="22" t="s">
         <v>102</v>
       </c>
@@ -8829,7 +8822,7 @@
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>123</v>
@@ -8848,7 +8841,7 @@
       </c>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A8" s="22" t="s">
         <v>102</v>
       </c>
@@ -8870,7 +8863,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>147</v>
@@ -8889,7 +8882,7 @@
       </c>
       <c r="O8" s="12"/>
     </row>
-    <row r="9" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A9" s="22" t="s">
         <v>102</v>
       </c>
@@ -8911,7 +8904,7 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>170</v>
@@ -8928,7 +8921,7 @@
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
     </row>
-    <row r="10" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>102</v>
       </c>
@@ -8950,7 +8943,7 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>184</v>
@@ -8969,7 +8962,7 @@
       </c>
       <c r="O10" s="12"/>
     </row>
-    <row r="11" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A11" s="22" t="s">
         <v>102</v>
       </c>
@@ -8991,7 +8984,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>196</v>
@@ -9012,7 +9005,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>206</v>
       </c>
@@ -9036,7 +9029,7 @@
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>221</v>
@@ -9051,7 +9044,7 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
     </row>
-    <row r="13" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>206</v>
       </c>
@@ -9073,7 +9066,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>237</v>
@@ -9088,7 +9081,7 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
     </row>
-    <row r="14" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A14" s="22" t="s">
         <v>206</v>
       </c>
@@ -9112,7 +9105,7 @@
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>241</v>
@@ -9127,7 +9120,7 @@
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
     </row>
-    <row r="15" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
@@ -9151,7 +9144,7 @@
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>254</v>
@@ -9166,7 +9159,7 @@
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
     </row>
-    <row r="16" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>206</v>
       </c>
@@ -9174,7 +9167,7 @@
         <v>211</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>220</v>
@@ -9190,7 +9183,7 @@
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>288</v>
@@ -9209,7 +9202,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>206</v>
       </c>
@@ -9233,7 +9226,7 @@
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>271</v>
@@ -9246,13 +9239,13 @@
         <v>273</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A18" s="22" t="s">
         <v>289</v>
       </c>
@@ -9272,7 +9265,7 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>324</v>
@@ -9287,7 +9280,7 @@
       <c r="N18" s="12"/>
       <c r="O18" s="12"/>
     </row>
-    <row r="19" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A19" s="22" t="s">
         <v>289</v>
       </c>
@@ -9305,7 +9298,7 @@
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>333</v>
@@ -9320,7 +9313,7 @@
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
     </row>
-    <row r="20" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>289</v>
       </c>
@@ -9338,7 +9331,7 @@
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>338</v>
@@ -9353,7 +9346,7 @@
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
     </row>
-    <row r="21" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A21" s="22" t="s">
         <v>289</v>
       </c>
@@ -9373,7 +9366,7 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>343</v>
@@ -9388,7 +9381,7 @@
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
     </row>
-    <row r="22" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A22" s="22" t="s">
         <v>289</v>
       </c>
@@ -9410,7 +9403,7 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>371</v>
@@ -9423,7 +9416,7 @@
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
     </row>
-    <row r="23" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A23" s="22" t="s">
         <v>289</v>
       </c>
@@ -9431,7 +9424,7 @@
         <v>305</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>306</v>
@@ -9445,7 +9438,7 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>378</v>
@@ -9460,7 +9453,7 @@
       </c>
       <c r="O23" s="12"/>
     </row>
-    <row r="24" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A24" s="22" t="s">
         <v>289</v>
       </c>
@@ -9480,7 +9473,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>423</v>
@@ -9493,7 +9486,7 @@
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
     </row>
-    <row r="25" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A25" s="22" t="s">
         <v>289</v>
       </c>
@@ -9513,7 +9506,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>424</v>
@@ -9528,7 +9521,7 @@
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
     </row>
-    <row r="26" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A26" s="22" t="s">
         <v>289</v>
       </c>
@@ -9548,7 +9541,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>425</v>
@@ -9563,7 +9556,7 @@
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
     </row>
-    <row r="27" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A27" s="22" t="s">
         <v>289</v>
       </c>
@@ -9583,7 +9576,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>385</v>
@@ -9598,7 +9591,7 @@
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
     </row>
-    <row r="28" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A28" s="22" t="s">
         <v>289</v>
       </c>
@@ -9622,7 +9615,7 @@
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>389</v>
@@ -9635,7 +9628,7 @@
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
     </row>
-    <row r="29" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A29" s="22" t="s">
         <v>289</v>
       </c>
@@ -9643,7 +9636,7 @@
         <v>319</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>320</v>
@@ -9659,7 +9652,7 @@
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>392</v>
@@ -9674,7 +9667,7 @@
       </c>
       <c r="O29" s="12"/>
     </row>
-    <row r="30" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A30" s="22" t="s">
         <v>394</v>
       </c>
@@ -9696,7 +9689,7 @@
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>421</v>
@@ -9713,7 +9706,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A31" s="22" t="s">
         <v>394</v>
       </c>
@@ -9733,7 +9726,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>427</v>
@@ -9752,7 +9745,7 @@
       </c>
       <c r="O31" s="12"/>
     </row>
-    <row r="32" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A32" s="22" t="s">
         <v>394</v>
       </c>
@@ -9772,7 +9765,7 @@
         <v>405</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="J32" s="12"/>
       <c r="K32" s="12"/>
@@ -9787,7 +9780,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A33" s="22" t="s">
         <v>394</v>
       </c>
@@ -9809,7 +9802,7 @@
         <v>30</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>434</v>
@@ -9826,7 +9819,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A34" s="22" t="s">
         <v>394</v>
       </c>
@@ -9846,7 +9839,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>441</v>
@@ -9861,7 +9854,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A35" s="22" t="s">
         <v>394</v>
       </c>
@@ -9883,7 +9876,7 @@
         <v>405</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>445</v>
@@ -9898,7 +9891,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A36" s="22" t="s">
         <v>394</v>
       </c>
@@ -9920,7 +9913,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>452</v>
@@ -9937,16 +9930,16 @@
         <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A37" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>418</v>
@@ -9957,7 +9950,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
@@ -9965,50 +9958,50 @@
         <v>53</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N37" s="12"/>
       <c r="O37" s="11" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="55" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="56" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="57" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="58" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="59" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="60" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="61" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="62" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="63" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="64" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="65" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="66" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="67" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="68" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="69" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="70" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="71" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="72" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="73" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="74" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="38" spans="1:15" ht="50" customHeight="1"/>
+    <row r="39" spans="1:15" ht="50" customHeight="1"/>
+    <row r="40" spans="1:15" ht="50" customHeight="1"/>
+    <row r="41" spans="1:15" ht="50" customHeight="1"/>
+    <row r="42" spans="1:15" ht="50" customHeight="1"/>
+    <row r="43" spans="1:15" ht="50" customHeight="1"/>
+    <row r="44" spans="1:15" ht="50" customHeight="1"/>
+    <row r="45" spans="1:15" ht="50" customHeight="1"/>
+    <row r="46" spans="1:15" ht="50" customHeight="1"/>
+    <row r="47" spans="1:15" ht="50" customHeight="1"/>
+    <row r="48" spans="1:15" ht="50" customHeight="1"/>
+    <row r="49" ht="50" customHeight="1"/>
+    <row r="50" ht="50" customHeight="1"/>
+    <row r="51" ht="50" customHeight="1"/>
+    <row r="52" ht="50" customHeight="1"/>
+    <row r="53" ht="50" customHeight="1"/>
+    <row r="54" ht="50" customHeight="1"/>
+    <row r="55" ht="50" customHeight="1"/>
+    <row r="56" ht="50" customHeight="1"/>
+    <row r="57" ht="50" customHeight="1"/>
+    <row r="58" ht="50" customHeight="1"/>
+    <row r="59" ht="50" customHeight="1"/>
+    <row r="60" ht="50" customHeight="1"/>
+    <row r="61" ht="50" customHeight="1"/>
+    <row r="62" ht="50" customHeight="1"/>
+    <row r="63" ht="50" customHeight="1"/>
+    <row r="64" ht="50" customHeight="1"/>
+    <row r="65" ht="50" customHeight="1"/>
+    <row r="66" ht="50" customHeight="1"/>
+    <row r="67" ht="50" customHeight="1"/>
+    <row r="68" ht="50" customHeight="1"/>
+    <row r="69" ht="50" customHeight="1"/>
+    <row r="70" ht="50" customHeight="1"/>
+    <row r="71" ht="50" customHeight="1"/>
+    <row r="72" ht="50" customHeight="1"/>
+    <row r="73" ht="50" customHeight="1"/>
+    <row r="74" ht="50" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10019,14 +10012,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347C379D-DB60-4D96-8211-0C66A7043ACA}">
   <dimension ref="A1:C296"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.58203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="43.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.58203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -10034,10 +10027,10 @@
         <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="3">
         <v>112</v>
       </c>
@@ -10045,7 +10038,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3">
       <c r="A3" s="3">
         <v>114</v>
       </c>
@@ -10053,7 +10046,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3">
       <c r="A4" s="3">
         <v>116</v>
       </c>
@@ -10061,63 +10054,63 @@
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3">
       <c r="A5" s="3">
         <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="3">
         <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="3">
         <v>152</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="3">
         <v>153</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="3">
         <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="3">
         <v>227</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="3">
         <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="3">
         <v>322</v>
       </c>
@@ -10125,7 +10118,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3">
       <c r="A13" s="3">
         <v>323</v>
       </c>
@@ -10133,7 +10126,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3">
       <c r="A14" s="3">
         <v>324</v>
       </c>
@@ -10141,7 +10134,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3">
       <c r="A15" s="3">
         <v>325</v>
       </c>
@@ -10149,7 +10142,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3">
       <c r="A16" s="3">
         <v>326</v>
       </c>
@@ -10157,7 +10150,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2">
       <c r="A17" s="3">
         <v>327</v>
       </c>
@@ -10165,7 +10158,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2">
       <c r="A18" s="3">
         <v>328</v>
       </c>
@@ -10173,7 +10166,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2">
       <c r="A19" s="3">
         <v>329</v>
       </c>
@@ -10181,7 +10174,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2">
       <c r="A20" s="3">
         <v>330</v>
       </c>
@@ -10189,7 +10182,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2">
       <c r="A21" s="3">
         <v>331</v>
       </c>
@@ -10197,7 +10190,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2">
       <c r="A22" s="3">
         <v>332</v>
       </c>
@@ -10205,7 +10198,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2">
       <c r="A23" s="3">
         <v>333</v>
       </c>
@@ -10213,7 +10206,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2">
       <c r="A24" s="3">
         <v>334</v>
       </c>
@@ -10221,7 +10214,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2">
       <c r="A25" s="3">
         <v>335</v>
       </c>
@@ -10229,7 +10222,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2">
       <c r="A26" s="3">
         <v>336</v>
       </c>
@@ -10237,7 +10230,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2">
       <c r="A27" s="3">
         <v>337</v>
       </c>
@@ -10245,7 +10238,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2">
       <c r="A28" s="3">
         <v>338</v>
       </c>
@@ -10253,7 +10246,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2">
       <c r="A29" s="3">
         <v>339</v>
       </c>
@@ -10261,7 +10254,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2">
       <c r="A30" s="3">
         <v>340</v>
       </c>
@@ -10269,7 +10262,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2">
       <c r="A31" s="3">
         <v>341</v>
       </c>
@@ -10277,15 +10270,15 @@
         <v>370</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2">
       <c r="A32" s="3">
         <v>916</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="3">
         <v>1077</v>
       </c>
@@ -10293,7 +10286,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2">
       <c r="A34" s="3">
         <v>1081</v>
       </c>
@@ -10301,7 +10294,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2">
       <c r="A35" s="3">
         <v>1083</v>
       </c>
@@ -10309,31 +10302,31 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2">
       <c r="A36" s="3">
         <v>1085</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="3">
         <v>1086</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="3">
         <v>1087</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="3">
         <v>1095</v>
       </c>
@@ -10341,7 +10334,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2">
       <c r="A40" s="3">
         <v>1096</v>
       </c>
@@ -10349,7 +10342,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2">
       <c r="A41" s="3">
         <v>1109</v>
       </c>
@@ -10357,7 +10350,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2">
       <c r="A42" s="3">
         <v>1110</v>
       </c>
@@ -10365,7 +10358,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2">
       <c r="A43" s="3">
         <v>1111</v>
       </c>
@@ -10373,31 +10366,31 @@
         <v>369</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2">
       <c r="A44" s="3">
         <v>1176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="3">
         <v>1294</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="3">
         <v>1295</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="3">
         <v>1325</v>
       </c>
@@ -10405,7 +10398,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2">
       <c r="A48" s="3">
         <v>1326</v>
       </c>
@@ -10413,7 +10406,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2">
       <c r="A49" s="3">
         <v>1327</v>
       </c>
@@ -10421,7 +10414,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2">
       <c r="A50" s="3">
         <v>1328</v>
       </c>
@@ -10429,7 +10422,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2">
       <c r="A51" s="3">
         <v>1329</v>
       </c>
@@ -10437,7 +10430,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2">
       <c r="A52" s="3">
         <v>1340</v>
       </c>
@@ -10445,7 +10438,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2">
       <c r="A53" s="3">
         <v>1341</v>
       </c>
@@ -10453,7 +10446,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2">
       <c r="A54" s="3">
         <v>1547</v>
       </c>
@@ -10461,7 +10454,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2">
       <c r="A55" s="3">
         <v>1548</v>
       </c>
@@ -10469,7 +10462,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2">
       <c r="A56" s="3">
         <v>1549</v>
       </c>
@@ -10477,7 +10470,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2">
       <c r="A57" s="3">
         <v>1550</v>
       </c>
@@ -10485,7 +10478,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2">
       <c r="A58" s="3">
         <v>1551</v>
       </c>
@@ -10493,7 +10486,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2">
       <c r="A59" s="3">
         <v>1709</v>
       </c>
@@ -10501,7 +10494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2">
       <c r="A60" s="3">
         <v>2250</v>
       </c>
@@ -10509,7 +10502,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2">
       <c r="A61" s="3">
         <v>2425</v>
       </c>
@@ -10517,7 +10510,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2">
       <c r="A62" s="3">
         <v>3317</v>
       </c>
@@ -10525,7 +10518,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2">
       <c r="A63" s="3">
         <v>3318</v>
       </c>
@@ -10533,7 +10526,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2">
       <c r="A64" s="3">
         <v>3319</v>
       </c>
@@ -10541,7 +10534,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3">
       <c r="A65" s="3">
         <v>3320</v>
       </c>
@@ -10549,7 +10542,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3">
       <c r="A66" s="3">
         <v>3321</v>
       </c>
@@ -10557,7 +10550,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3">
       <c r="A67" s="3">
         <v>3322</v>
       </c>
@@ -10565,7 +10558,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3">
       <c r="A68" s="3">
         <v>3323</v>
       </c>
@@ -10573,7 +10566,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3">
       <c r="A69" s="3">
         <v>3324</v>
       </c>
@@ -10581,7 +10574,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3">
       <c r="A70" s="3">
         <v>3325</v>
       </c>
@@ -10589,18 +10582,18 @@
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:3">
       <c r="A71" s="3">
         <v>3535</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="3">
         <v>3700</v>
       </c>
@@ -10608,7 +10601,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:3">
       <c r="A73" s="3">
         <v>3701</v>
       </c>
@@ -10616,7 +10609,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:3">
       <c r="A74" s="3">
         <v>3702</v>
       </c>
@@ -10624,7 +10617,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:3">
       <c r="A75" s="3">
         <v>3795</v>
       </c>
@@ -10632,7 +10625,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:3">
       <c r="A76" s="3">
         <v>3826</v>
       </c>
@@ -10640,7 +10633,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:3">
       <c r="A77" s="3">
         <v>3827</v>
       </c>
@@ -10648,7 +10641,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:3">
       <c r="A78" s="3">
         <v>3891</v>
       </c>
@@ -10656,7 +10649,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:3">
       <c r="A79" s="3">
         <v>3911</v>
       </c>
@@ -10664,7 +10657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:3">
       <c r="A80" s="3">
         <v>3971</v>
       </c>
@@ -10672,7 +10665,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2">
       <c r="A81" s="3">
         <v>3973</v>
       </c>
@@ -10680,7 +10673,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2">
       <c r="A82" s="3">
         <v>3974</v>
       </c>
@@ -10688,7 +10681,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2">
       <c r="A83" s="3">
         <v>4014</v>
       </c>
@@ -10696,7 +10689,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2">
       <c r="A84" s="3">
         <v>4369</v>
       </c>
@@ -10704,7 +10697,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2">
       <c r="A85" s="3">
         <v>4370</v>
       </c>
@@ -10712,7 +10705,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2">
       <c r="A86" s="3">
         <v>4371</v>
       </c>
@@ -10720,7 +10713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2">
       <c r="A87" s="3">
         <v>4372</v>
       </c>
@@ -10728,7 +10721,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2">
       <c r="A88" s="3">
         <v>4373</v>
       </c>
@@ -10736,7 +10729,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2">
       <c r="A89" s="3">
         <v>5739</v>
       </c>
@@ -10744,7 +10737,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2">
       <c r="A90" s="3">
         <v>6073</v>
       </c>
@@ -10752,7 +10745,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2">
       <c r="A91" s="3">
         <v>6074</v>
       </c>
@@ -10760,7 +10753,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2">
       <c r="A92" s="3">
         <v>6075</v>
       </c>
@@ -10768,7 +10761,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2">
       <c r="A93" s="3">
         <v>6076</v>
       </c>
@@ -10776,7 +10769,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2">
       <c r="A94" s="3">
         <v>6077</v>
       </c>
@@ -10784,7 +10777,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2">
       <c r="A95" s="3">
         <v>6178</v>
       </c>
@@ -10792,7 +10785,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2">
       <c r="A96" s="3">
         <v>6522</v>
       </c>
@@ -10800,7 +10793,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2">
       <c r="A97" s="3">
         <v>6607</v>
       </c>
@@ -10808,7 +10801,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2">
       <c r="A98" s="3">
         <v>6608</v>
       </c>
@@ -10816,7 +10809,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2">
       <c r="A99" s="3">
         <v>6609</v>
       </c>
@@ -10824,7 +10817,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2">
       <c r="A100" s="3">
         <v>6878</v>
       </c>
@@ -10832,7 +10825,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2">
       <c r="A101" s="3">
         <v>7020</v>
       </c>
@@ -10840,7 +10833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2">
       <c r="A102" s="3">
         <v>7021</v>
       </c>
@@ -10848,7 +10841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2">
       <c r="A103" s="3">
         <v>7022</v>
       </c>
@@ -10856,7 +10849,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2">
       <c r="A104" s="3">
         <v>7023</v>
       </c>
@@ -10864,7 +10857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2">
       <c r="A105" s="3">
         <v>7042</v>
       </c>
@@ -10872,7 +10865,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:2">
       <c r="A106" s="3">
         <v>7493</v>
       </c>
@@ -10880,7 +10873,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2">
       <c r="A107" s="3">
         <v>7680</v>
       </c>
@@ -10888,7 +10881,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2">
       <c r="A108" s="3">
         <v>7681</v>
       </c>
@@ -10896,7 +10889,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:2">
       <c r="A109" s="3">
         <v>7684</v>
       </c>
@@ -10904,7 +10897,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:2">
       <c r="A110" s="3">
         <v>7686</v>
       </c>
@@ -10912,58 +10905,58 @@
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2">
       <c r="A111" s="3">
         <v>7757</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112" s="3">
         <v>7758</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="3">
         <v>7759</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="3">
         <v>7760</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="3">
         <v>7761</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="3">
         <v>7851</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="3">
         <v>8298</v>
       </c>
@@ -10971,7 +10964,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:3">
       <c r="A118" s="3">
         <v>8551</v>
       </c>
@@ -10979,7 +10972,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3">
       <c r="A119" s="3">
         <v>8552</v>
       </c>
@@ -10987,7 +10980,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3">
       <c r="A120" s="3">
         <v>8553</v>
       </c>
@@ -10995,7 +10988,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3">
       <c r="A121" s="3">
         <v>8554</v>
       </c>
@@ -11003,7 +10996,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3">
       <c r="A122" s="3">
         <v>8555</v>
       </c>
@@ -11011,7 +11004,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3">
       <c r="A123" s="3">
         <v>8728</v>
       </c>
@@ -11019,7 +11012,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3">
       <c r="A124" s="3">
         <v>8914</v>
       </c>
@@ -11027,21 +11020,21 @@
         <v>322</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="3">
         <v>8915</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126" s="3">
         <v>8916</v>
       </c>
@@ -11049,7 +11042,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3">
       <c r="A127" s="3">
         <v>9000</v>
       </c>
@@ -11057,7 +11050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:3">
       <c r="A128" s="3">
         <v>9227</v>
       </c>
@@ -11065,21 +11058,21 @@
         <v>331</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="3">
         <v>9228</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
       <c r="A130" s="3">
         <v>9229</v>
       </c>
@@ -11087,7 +11080,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:3">
       <c r="A131" s="3">
         <v>9454</v>
       </c>
@@ -11095,7 +11088,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:3">
       <c r="A132" s="3">
         <v>9455</v>
       </c>
@@ -11103,21 +11096,21 @@
         <v>336</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
       <c r="A133" s="3">
         <v>9456</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
       <c r="A134" s="3">
         <v>9457</v>
       </c>
@@ -11125,7 +11118,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3">
       <c r="A135" s="3">
         <v>9534</v>
       </c>
@@ -11133,7 +11126,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3">
       <c r="A136" s="3">
         <v>9716</v>
       </c>
@@ -11141,21 +11134,21 @@
         <v>341</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
       <c r="A137" s="3">
         <v>9718</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
       <c r="A138" s="3">
         <v>9827</v>
       </c>
@@ -11163,69 +11156,69 @@
         <v>342</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3">
       <c r="A139" s="3">
         <v>9870</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
       <c r="A140" s="3">
         <v>9872</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="3">
         <v>10007</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
       <c r="A142" s="3">
         <v>10008</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="3">
         <v>10009</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
       <c r="A144" s="3">
         <v>10010</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
       <c r="A145" s="3">
         <v>10011</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
       <c r="A146" s="3">
         <v>10022</v>
       </c>
@@ -11233,7 +11226,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:3">
       <c r="A147" s="3">
         <v>10023</v>
       </c>
@@ -11241,7 +11234,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3">
       <c r="A148" s="3">
         <v>10024</v>
       </c>
@@ -11249,7 +11242,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3">
       <c r="A149" s="3">
         <v>10025</v>
       </c>
@@ -11257,7 +11250,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3">
       <c r="A150" s="3">
         <v>10026</v>
       </c>
@@ -11265,7 +11258,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3">
       <c r="A151" s="3">
         <v>10114</v>
       </c>
@@ -11273,51 +11266,51 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3">
       <c r="A152" s="3">
         <v>10297</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
       <c r="A153" s="3">
         <v>10298</v>
       </c>
       <c r="B153" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="C153" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="154" spans="1:3">
       <c r="A154" s="3">
         <v>10301</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
       <c r="A155" s="3">
         <v>10304</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156" s="3">
         <v>10512</v>
       </c>
@@ -11325,7 +11318,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3">
       <c r="A157" s="3">
         <v>10513</v>
       </c>
@@ -11333,7 +11326,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3">
       <c r="A158" s="3">
         <v>10514</v>
       </c>
@@ -11341,7 +11334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3">
       <c r="A159" s="3">
         <v>10515</v>
       </c>
@@ -11349,7 +11342,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3">
       <c r="A160" s="3">
         <v>10516</v>
       </c>
@@ -11357,7 +11350,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:3">
       <c r="A161" s="3">
         <v>10517</v>
       </c>
@@ -11365,7 +11358,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:3">
       <c r="A162" s="3">
         <v>10518</v>
       </c>
@@ -11373,7 +11366,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:3">
       <c r="A163" s="3">
         <v>10519</v>
       </c>
@@ -11381,7 +11374,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:3">
       <c r="A164" s="3">
         <v>10520</v>
       </c>
@@ -11389,7 +11382,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:3">
       <c r="A165" s="3">
         <v>10521</v>
       </c>
@@ -11397,18 +11390,18 @@
         <v>183</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:3">
       <c r="A166" s="3">
         <v>10522</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
       <c r="A167" s="3">
         <v>10528</v>
       </c>
@@ -11416,7 +11409,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:3">
       <c r="A168" s="3">
         <v>10529</v>
       </c>
@@ -11424,7 +11417,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:3">
       <c r="A169" s="3">
         <v>10530</v>
       </c>
@@ -11432,23 +11425,23 @@
         <v>131</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:3">
       <c r="A170" s="3">
         <v>10531</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
       <c r="A171" s="3">
         <v>10532</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
       <c r="A172" s="3">
         <v>10533</v>
       </c>
@@ -11456,7 +11449,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:3">
       <c r="A173" s="3">
         <v>11037</v>
       </c>
@@ -11464,7 +11457,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:3">
       <c r="A174" s="3">
         <v>11038</v>
       </c>
@@ -11472,7 +11465,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:3">
       <c r="A175" s="3">
         <v>11039</v>
       </c>
@@ -11480,7 +11473,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:3">
       <c r="A176" s="3">
         <v>11040</v>
       </c>
@@ -11488,7 +11481,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:3">
       <c r="A177" s="3">
         <v>11046</v>
       </c>
@@ -11496,7 +11489,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:3">
       <c r="A178" s="3">
         <v>11108</v>
       </c>
@@ -11504,18 +11497,18 @@
         <v>167</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:3">
       <c r="A179" s="3">
         <v>11115</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
       <c r="A180" s="3">
         <v>11119</v>
       </c>
@@ -11523,18 +11516,18 @@
         <v>222</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:3">
       <c r="A181" s="3">
         <v>11192</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
       <c r="A182" s="3">
         <v>11196</v>
       </c>
@@ -11542,18 +11535,18 @@
         <v>239</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:3">
       <c r="A183" s="3">
         <v>11203</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
       <c r="A184" s="3">
         <v>11207</v>
       </c>
@@ -11561,15 +11554,15 @@
         <v>243</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:3">
       <c r="A185" s="3">
         <v>11216</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
       <c r="A186" s="3">
         <v>11217</v>
       </c>
@@ -11577,7 +11570,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:3">
       <c r="A187" s="3">
         <v>11218</v>
       </c>
@@ -11585,18 +11578,18 @@
         <v>461</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:3">
       <c r="A188" s="3">
         <v>11548</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" s="3">
         <v>11552</v>
       </c>
@@ -11604,18 +11597,18 @@
         <v>244</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:3">
       <c r="A190" s="3">
         <v>11553</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
       <c r="A191" s="3">
         <v>11556</v>
       </c>
@@ -11623,15 +11616,15 @@
         <v>256</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:3">
       <c r="A192" s="3">
         <v>11557</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
       <c r="A193" s="3">
         <v>11559</v>
       </c>
@@ -11639,15 +11632,15 @@
         <v>257</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:3">
       <c r="A194" s="3">
         <v>11560</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
       <c r="A195" s="3">
         <v>11562</v>
       </c>
@@ -11655,15 +11648,15 @@
         <v>258</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:3">
       <c r="A196" s="3">
         <v>11563</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
       <c r="A197" s="3">
         <v>11565</v>
       </c>
@@ -11671,15 +11664,15 @@
         <v>259</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:3">
       <c r="A198" s="3">
         <v>11566</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
       <c r="A199" s="3">
         <v>11568</v>
       </c>
@@ -11687,7 +11680,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:3">
       <c r="A200" s="3">
         <v>11588</v>
       </c>
@@ -11695,23 +11688,23 @@
         <v>245</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:3">
       <c r="A201" s="3">
         <v>12112</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
       <c r="A202" s="3">
         <v>12113</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
       <c r="A203" s="3">
         <v>12114</v>
       </c>
@@ -11719,18 +11712,18 @@
         <v>459</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:3">
       <c r="A204" s="3">
         <v>12252</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
       <c r="A205" s="3">
         <v>12257</v>
       </c>
@@ -11738,7 +11731,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:3">
       <c r="A206" s="3">
         <v>12258</v>
       </c>
@@ -11746,15 +11739,15 @@
         <v>269</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:3">
       <c r="A207" s="3">
         <v>12260</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
       <c r="A208" s="3">
         <v>12261</v>
       </c>
@@ -11762,23 +11755,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:3">
       <c r="A209" s="3">
         <v>12343</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
       <c r="A210" s="3">
         <v>12344</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
       <c r="A211" s="3">
         <v>12345</v>
       </c>
@@ -11786,7 +11779,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:3">
       <c r="A212" s="3">
         <v>12346</v>
       </c>
@@ -11794,18 +11787,18 @@
         <v>458</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:3">
       <c r="A213" s="3">
         <v>12685</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
       <c r="A214" s="3">
         <v>12691</v>
       </c>
@@ -11813,7 +11806,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:3">
       <c r="A215" s="3">
         <v>12692</v>
       </c>
@@ -11821,7 +11814,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:3">
       <c r="A216" s="3">
         <v>12693</v>
       </c>
@@ -11829,23 +11822,23 @@
         <v>144</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:3">
       <c r="A217" s="3">
         <v>12694</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
       <c r="A218" s="3">
         <v>12695</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
       <c r="A219" s="3">
         <v>12696</v>
       </c>
@@ -11853,7 +11846,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:3">
       <c r="A220" s="3">
         <v>12697</v>
       </c>
@@ -11861,18 +11854,18 @@
         <v>146</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:3">
       <c r="A221" s="3">
         <v>12857</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
       <c r="A222" s="3">
         <v>12863</v>
       </c>
@@ -11880,7 +11873,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:3">
       <c r="A223" s="3">
         <v>12864</v>
       </c>
@@ -11888,7 +11881,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:3">
       <c r="A224" s="3">
         <v>12865</v>
       </c>
@@ -11896,7 +11889,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:3">
       <c r="A225" s="3">
         <v>12866</v>
       </c>
@@ -11904,23 +11897,23 @@
         <v>156</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:3">
       <c r="A226" s="3">
         <v>12867</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
       <c r="A227" s="3">
         <v>12868</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
       <c r="A228" s="3">
         <v>12869</v>
       </c>
@@ -11928,26 +11921,26 @@
         <v>157</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:3">
       <c r="A229" s="3">
         <v>13045</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
       <c r="A230" s="3">
         <v>13046</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
       <c r="A231" s="3">
         <v>13047</v>
       </c>
@@ -11955,7 +11948,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:3">
       <c r="A232" s="3">
         <v>13048</v>
       </c>
@@ -11963,18 +11956,18 @@
         <v>440</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:3">
       <c r="A233" s="3">
         <v>13049</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
       <c r="A234" s="3">
         <v>13055</v>
       </c>
@@ -11982,7 +11975,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:3">
       <c r="A235" s="3">
         <v>13056</v>
       </c>
@@ -11990,7 +11983,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:3">
       <c r="A236" s="3">
         <v>13057</v>
       </c>
@@ -11998,23 +11991,23 @@
         <v>175</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:3">
       <c r="A237" s="3">
         <v>13058</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
       <c r="A238" s="3">
         <v>13059</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
       <c r="A239" s="3">
         <v>13060</v>
       </c>
@@ -12022,15 +12015,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:3">
       <c r="A240" s="3">
         <v>13294</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
       <c r="A241" s="3">
         <v>13295</v>
       </c>
@@ -12038,23 +12031,23 @@
         <v>193</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:3">
       <c r="A242" s="3">
         <v>13301</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
       <c r="A243" s="3">
         <v>13302</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
       <c r="A244" s="3">
         <v>13303</v>
       </c>
@@ -12062,7 +12055,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:3">
       <c r="A245" s="3">
         <v>13304</v>
       </c>
@@ -12070,18 +12063,18 @@
         <v>456</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:3">
       <c r="A246" s="3">
         <v>13375</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
       <c r="A247" s="3">
         <v>13381</v>
       </c>
@@ -12089,7 +12082,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:3">
       <c r="A248" s="3">
         <v>13382</v>
       </c>
@@ -12097,7 +12090,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:3">
       <c r="A249" s="3">
         <v>13383</v>
       </c>
@@ -12105,7 +12098,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:3">
       <c r="A250" s="3">
         <v>13384</v>
       </c>
@@ -12113,34 +12106,34 @@
         <v>192</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:3">
       <c r="A251" s="3">
         <v>13385</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
       <c r="A252" s="3">
         <v>13494</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
       <c r="A253" s="3">
         <v>13498</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
       <c r="A254" s="3">
         <v>13499</v>
       </c>
@@ -12148,7 +12141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:3">
       <c r="A255" s="3">
         <v>13500</v>
       </c>
@@ -12156,7 +12149,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:3">
       <c r="A256" s="3">
         <v>13501</v>
       </c>
@@ -12164,15 +12157,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:3">
       <c r="A257" s="3">
         <v>13502</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
       <c r="A258" s="3">
         <v>13503</v>
       </c>
@@ -12180,26 +12173,26 @@
         <v>87</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:3">
       <c r="A259" s="3">
         <v>13585</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
       <c r="A260" s="3">
         <v>13589</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
       <c r="A261" s="3">
         <v>13590</v>
       </c>
@@ -12207,7 +12200,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:3">
       <c r="A262" s="3">
         <v>13591</v>
       </c>
@@ -12215,7 +12208,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:3">
       <c r="A263" s="3">
         <v>13592</v>
       </c>
@@ -12223,15 +12216,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:3">
       <c r="A264" s="3">
         <v>13593</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
       <c r="A265" s="3">
         <v>13594</v>
       </c>
@@ -12239,7 +12232,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:3">
       <c r="A266" s="3">
         <v>13667</v>
       </c>
@@ -12247,26 +12240,26 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:3">
       <c r="A267" s="3">
         <v>13794</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
       <c r="A268" s="3">
         <v>13798</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
       <c r="A269" s="3">
         <v>13799</v>
       </c>
@@ -12274,7 +12267,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:3">
       <c r="A270" s="3">
         <v>13800</v>
       </c>
@@ -12282,7 +12275,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:3">
       <c r="A271" s="3">
         <v>13801</v>
       </c>
@@ -12290,15 +12283,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:3">
       <c r="A272" s="3">
         <v>13802</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
       <c r="A273" s="3">
         <v>13803</v>
       </c>
@@ -12306,26 +12299,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:3">
       <c r="A274" s="3">
         <v>13816</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
       <c r="A275" s="3">
         <v>13820</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
       <c r="A276" s="3">
         <v>13821</v>
       </c>
@@ -12333,7 +12326,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:3">
       <c r="A277" s="3">
         <v>13822</v>
       </c>
@@ -12341,7 +12334,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:3">
       <c r="A278" s="3">
         <v>13823</v>
       </c>
@@ -12349,15 +12342,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:3">
       <c r="A279" s="3">
         <v>13824</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
       <c r="A280" s="3">
         <v>13825</v>
       </c>
@@ -12365,26 +12358,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:3">
       <c r="A281" s="3">
         <v>14018</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
       <c r="A282" s="3">
         <v>14022</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
       <c r="A283" s="3">
         <v>14023</v>
       </c>
@@ -12392,7 +12385,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:3">
       <c r="A284" s="3">
         <v>14024</v>
       </c>
@@ -12400,7 +12393,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:3">
       <c r="A285" s="3">
         <v>14025</v>
       </c>
@@ -12408,15 +12401,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:3">
       <c r="A286" s="3">
         <v>14026</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
       <c r="A287" s="3">
         <v>14027</v>
       </c>
@@ -12424,79 +12417,79 @@
         <v>95</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:3">
       <c r="A288" s="3">
         <v>14121</v>
       </c>
       <c r="B288" s="23" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
       <c r="A289" s="3">
         <v>14122</v>
       </c>
       <c r="B289" s="23" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
       <c r="A290" s="3">
         <v>14123</v>
       </c>
       <c r="B290" s="23" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
       <c r="A291" s="3">
         <v>14124</v>
       </c>
       <c r="B291" s="23" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
       <c r="A292" s="3">
         <v>14125</v>
       </c>
       <c r="B292" s="23" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
       <c r="A293" s="3">
         <v>14126</v>
       </c>
       <c r="B293" s="23" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
       <c r="A294" s="3">
         <v>14127</v>
       </c>
       <c r="B294" s="23" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
       <c r="A295" s="3">
         <v>14128</v>
       </c>
       <c r="B295" s="23" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
       <c r="A296" s="3">
         <v>14131</v>
       </c>
       <c r="B296" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C296" s="3" t="s">
         <v>784</v>
-      </c>
-      <c r="C296" s="3" t="s">
-        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -12511,7 +12504,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74834FCE-95F4-4591-933C-7E036125508A}">
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="17.33203125" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="17.33203125" defaultRowHeight="50" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="50.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
@@ -12520,973 +12513,973 @@
     <col min="5" max="5" width="17.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="24" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" s="24" customFormat="1" ht="50" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D1" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>480</v>
       </c>
-      <c r="E1" s="24" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="50" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="50" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="50" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="50" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="50" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="50" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="50" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="50" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="50" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="50" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="50" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="50" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="50" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="50" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="50" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="50" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="50" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="50" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="50" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="50" customHeight="1">
+      <c r="A21" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="50" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="50" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="50" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="50" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="50" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="50" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>595</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="50" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="50" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="50" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="50" customHeight="1">
+      <c r="A31" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="50" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="50" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="50" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="50" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="50" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="50" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="50" customHeight="1">
       <c r="A38" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="50" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1" t="s">
+      <c r="E39" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="50" customHeight="1">
+      <c r="A40" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="B40" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="50" customHeight="1">
       <c r="A41" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="D41" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="50" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1" t="s">
+      <c r="E42" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="50" customHeight="1">
+      <c r="A43" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="50" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="50" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="50" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>660</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="50" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="50" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="50" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="50" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="50" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="50" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="50" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="50" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="50" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="50" customHeight="1">
       <c r="A56" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="50" customHeight="1">
+      <c r="A57" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -13498,14 +13491,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FCBD9B-5783-443C-87DE-4B13994EA8C3}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="17.08203125" style="16" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" s="16" t="s">
         <v>201</v>
       </c>
@@ -13516,7 +13509,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3">
       <c r="A2" s="17">
         <v>46264</v>
       </c>
@@ -13536,12 +13529,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA087EF-D4CB-4508-81E0-4C5741605FD2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="15.58203125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>462</v>
       </c>
@@ -13552,15 +13545,9 @@
         <v>464</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>465</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E949EAD-BDA6-49C3-B5EA-247D90FB3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A863F79-B83D-4F29-8FE1-9421A6E10720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4130" yWindow="1450" windowWidth="14400" windowHeight="8170" activeTab="4" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="787">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -7390,6 +7390,13 @@
   </si>
   <si>
     <t>14131_1</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>追加日</t>
+    <rPh sb="0" eb="3">
+      <t>ツイカビ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -7779,7 +7786,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -7944,6 +7951,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -8073,7 +8089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8155,6 +8171,24 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -8531,1451 +8565,1563 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF7705B-378C-43E5-944D-EC87F141ACDD}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="20.58203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="156.4140625" style="15" customWidth="1"/>
-    <col min="4" max="8" width="25.58203125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="50.58203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="163.75" style="14" customWidth="1"/>
-    <col min="11" max="11" width="71.1640625" style="14" customWidth="1"/>
-    <col min="12" max="12" width="71.08203125" style="14" customWidth="1"/>
-    <col min="13" max="13" width="255.5" style="14" customWidth="1"/>
-    <col min="14" max="14" width="151.1640625" style="14" customWidth="1"/>
-    <col min="15" max="15" width="104.1640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="156.4140625" style="15" customWidth="1"/>
+    <col min="5" max="9" width="25.58203125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="50.58203125" style="15" customWidth="1"/>
+    <col min="11" max="11" width="163.75" style="14" customWidth="1"/>
+    <col min="12" max="12" width="71.1640625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="71.08203125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="255.5" style="14" customWidth="1"/>
+    <col min="15" max="15" width="151.1640625" style="14" customWidth="1"/>
+    <col min="16" max="16" width="104.1640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="1" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="27" t="s">
+        <v>786</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="2" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="26">
+        <v>46121</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="10">
+      <c r="G2" s="10">
         <v>2970</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10" t="s">
         <v>716</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="12"/>
+      <c r="M2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="12"/>
       <c r="O2" s="12"/>
-    </row>
-    <row r="3" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P2" s="12"/>
+    </row>
+    <row r="3" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="26">
+        <v>46202</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="10">
+      <c r="G3" s="10">
         <v>2970</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="12"/>
       <c r="O3" s="12"/>
-    </row>
-    <row r="4" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="26">
+        <v>46091</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="10">
+      <c r="G4" s="10">
         <v>2970</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="L4" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="M4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
-    </row>
-    <row r="5" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="26">
+        <v>46183</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="10">
+      <c r="G5" s="10">
         <v>6666</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
         <v>713</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="L5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="12"/>
+      <c r="P5" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="6" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>686</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="26">
+        <v>46267</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="10">
         <v>2970</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>30</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="J6" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="L6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="N6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12"/>
+      <c r="P6" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="7" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A7" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="26">
+        <v>45785</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="10">
         <v>2970</v>
       </c>
-      <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="O7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="O7" s="12"/>
-    </row>
-    <row r="8" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A8" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="26">
+        <v>45856</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="10">
         <v>2970</v>
       </c>
-      <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="M8" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="N8" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="O8" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="O8" s="12"/>
-    </row>
-    <row r="9" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A9" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="26">
+        <v>45912</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="10">
         <v>7777</v>
       </c>
-      <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
-    </row>
-    <row r="10" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="26">
+        <v>45996</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="10">
+      <c r="G10" s="10">
         <v>5000</v>
       </c>
-      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="9"/>
+      <c r="J10" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="L10" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="M10" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="N10" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="O10" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="O10" s="12"/>
-    </row>
-    <row r="11" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A11" s="22" t="s">
         <v>102</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="26">
+        <v>46063</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="10">
+      <c r="G11" s="10">
         <v>9999</v>
       </c>
-      <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="N11" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="P11" s="11" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="12" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="29">
+        <v>45399</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="10">
+      <c r="G12" s="10">
         <v>2970</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12"/>
+      <c r="N12" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
-    </row>
-    <row r="13" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="26">
+        <v>45457</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F13" s="10">
+      <c r="G13" s="10">
         <v>2970</v>
       </c>
-      <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="9"/>
+      <c r="J13" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="L13" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="12"/>
+      <c r="N13" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
-    </row>
-    <row r="14" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A14" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="26">
+        <v>45520</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F14" s="10">
+      <c r="G14" s="10">
         <v>2970</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12"/>
+      <c r="N14" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="N14" s="12"/>
       <c r="O14" s="12"/>
-    </row>
-    <row r="15" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A15" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="26">
+        <v>45576</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="F15" s="10">
+      <c r="G15" s="10">
         <v>6600</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="L15" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="12"/>
+      <c r="N15" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="N15" s="12"/>
       <c r="O15" s="12"/>
-    </row>
-    <row r="16" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="26">
+        <v>45645</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F16" s="10">
+      <c r="G16" s="10">
         <v>5555</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="M16" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="N16" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="12"/>
+      <c r="P16" s="11" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="17" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>206</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="26">
+        <v>45726</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F17" s="10">
+      <c r="G17" s="10">
         <v>7777</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="12"/>
+      <c r="N17" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="O17" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="O17" s="21" t="s">
+      <c r="P17" s="21" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="18" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A18" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="26">
+        <v>44756</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F18" s="10">
+      <c r="G18" s="10">
         <v>2970</v>
       </c>
-      <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="L18" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="12"/>
+      <c r="N18" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="N18" s="12"/>
       <c r="O18" s="12"/>
-    </row>
-    <row r="19" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A19" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="26">
+        <v>44799</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="12"/>
+      <c r="N19" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="N19" s="12"/>
       <c r="O19" s="12"/>
-    </row>
-    <row r="20" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P19" s="12"/>
+    </row>
+    <row r="20" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="26">
+        <v>44879</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="L20" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="11" t="s">
+      <c r="M20" s="12"/>
+      <c r="N20" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="N20" s="12"/>
       <c r="O20" s="12"/>
-    </row>
-    <row r="21" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A21" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="26">
+        <v>44979</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="F21" s="10">
+      <c r="G21" s="10">
         <v>2970</v>
       </c>
-      <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="12"/>
+      <c r="N21" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="N21" s="12"/>
       <c r="O21" s="12"/>
-    </row>
-    <row r="22" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P21" s="12"/>
+    </row>
+    <row r="22" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A22" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="26">
+        <v>45047</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="F22" s="10">
+      <c r="G22" s="10">
         <v>2970</v>
       </c>
-      <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="K22" s="12"/>
       <c r="L22" s="12"/>
-      <c r="M22" s="11" t="s">
+      <c r="M22" s="12"/>
+      <c r="N22" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="N22" s="12"/>
       <c r="O22" s="12"/>
-    </row>
-    <row r="23" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A23" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="26">
+        <v>45365</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F23" s="10">
+      <c r="G23" s="10">
         <v>2970</v>
       </c>
-      <c r="G23" s="9"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="K23" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="K23" s="12"/>
       <c r="L23" s="12"/>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="12"/>
+      <c r="N23" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="O23" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="O23" s="12"/>
-    </row>
-    <row r="24" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P23" s="12"/>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A24" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="26">
+        <v>44914</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F24" s="10">
+      <c r="G24" s="10">
         <v>2970</v>
       </c>
-      <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="K24" s="12"/>
       <c r="L24" s="12"/>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="12"/>
+      <c r="N24" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="N24" s="12"/>
       <c r="O24" s="12"/>
-    </row>
-    <row r="25" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A25" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="26">
+        <v>45070</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="F25" s="10">
+      <c r="G25" s="10">
         <v>2970</v>
       </c>
-      <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="9"/>
+      <c r="J25" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="K25" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="L25" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="12"/>
+      <c r="N25" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="N25" s="12"/>
       <c r="O25" s="12"/>
-    </row>
-    <row r="26" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P25" s="12"/>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A26" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="26">
+        <v>45135</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="F26" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="F26" s="10">
+      <c r="G26" s="10">
         <v>2970</v>
       </c>
-      <c r="G26" s="9"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="9"/>
+      <c r="J26" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="12"/>
+      <c r="N26" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="N26" s="12"/>
       <c r="O26" s="12"/>
-    </row>
-    <row r="27" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P26" s="12"/>
+    </row>
+    <row r="27" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A27" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9" t="s">
+      <c r="C27" s="26">
+        <v>45239</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="F27" s="10">
+      <c r="G27" s="10">
         <v>2970</v>
       </c>
-      <c r="G27" s="9"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="9"/>
+      <c r="J27" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="12"/>
+      <c r="N27" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="N27" s="12"/>
       <c r="O27" s="12"/>
-    </row>
-    <row r="28" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P27" s="12"/>
+    </row>
+    <row r="28" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A28" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="26">
+        <v>45283</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="F28" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="F28" s="10">
+      <c r="G28" s="10">
         <v>2970</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="9"/>
+      <c r="J28" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="K28" s="12"/>
       <c r="L28" s="12"/>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="12"/>
+      <c r="N28" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="N28" s="12"/>
       <c r="O28" s="12"/>
-    </row>
-    <row r="29" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A29" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="26">
+        <v>45674</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F29" s="10">
+      <c r="G29" s="10">
         <v>7777</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="9"/>
+      <c r="J29" s="9" t="s">
         <v>768</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="K29" s="12"/>
       <c r="L29" s="12"/>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="12"/>
+      <c r="N29" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="O29" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="O29" s="12"/>
-    </row>
-    <row r="30" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A30" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="26">
+        <v>45618</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="E30" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="9"/>
+      <c r="H30" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="9"/>
+      <c r="J30" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="K30" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="K30" s="12"/>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12"/>
+      <c r="M30" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="M30" s="12"/>
-      <c r="N30" s="11" t="s">
+      <c r="N30" s="12"/>
+      <c r="O30" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="P30" s="11" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="31" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A31" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="26">
+        <v>45758</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="F31" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="K31" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="N31" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="O31" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="O31" s="12"/>
-    </row>
-    <row r="32" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="P31" s="12"/>
+    </row>
+    <row r="32" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A32" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9" t="s">
+      <c r="C32" s="26">
+        <v>45924</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="J32" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="J32" s="12"/>
       <c r="K32" s="12"/>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="12"/>
+      <c r="M32" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="M32" s="12"/>
-      <c r="N32" s="11" t="s">
+      <c r="N32" s="12"/>
+      <c r="O32" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="P32" s="11" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="33" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A33" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="26">
+        <v>45956</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="9">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9">
         <v>30</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="J33" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="J33" s="11" t="s">
+      <c r="K33" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12"/>
+      <c r="M33" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="M33" s="12"/>
-      <c r="N33" s="11" t="s">
+      <c r="N33" s="12"/>
+      <c r="O33" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="P33" s="11" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="34" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A34" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="26">
+        <v>46013</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="9"/>
+      <c r="J34" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="K34" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="K34" s="12"/>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="12"/>
+      <c r="M34" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="M34" s="12"/>
       <c r="N34" s="12"/>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="12"/>
+      <c r="P34" s="11" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="35" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A35" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="26">
+        <v>46041</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="J35" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="K35" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="K35" s="12"/>
       <c r="L35" s="12"/>
       <c r="M35" s="12"/>
-      <c r="N35" s="11" t="s">
+      <c r="N35" s="12"/>
+      <c r="O35" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="P35" s="11" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="36" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A36" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="30">
+        <v>46161</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="F36" s="9"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="9">
+      <c r="H36" s="9"/>
+      <c r="I36" s="9">
         <v>30</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="J36" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="K36" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="K36" s="12"/>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="12"/>
+      <c r="M36" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="M36" s="12"/>
-      <c r="N36" s="11" t="s">
+      <c r="N36" s="12"/>
+      <c r="O36" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="O36" s="11" t="s">
+      <c r="P36" s="11" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="5" customFormat="1" ht="50" customHeight="1">
+    <row r="37" spans="1:16" s="5" customFormat="1" ht="50" customHeight="1">
       <c r="A37" s="22" t="s">
         <v>394</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9" t="s">
+      <c r="C37" s="26">
+        <v>46305</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="F37" s="9"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="9">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9">
         <v>30</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="J37" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="J37" s="12"/>
       <c r="K37" s="12"/>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12"/>
+      <c r="M37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="N37" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="N37" s="12"/>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="12"/>
+      <c r="P37" s="11" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="50" customHeight="1"/>
-    <row r="39" spans="1:15" ht="50" customHeight="1"/>
-    <row r="40" spans="1:15" ht="50" customHeight="1"/>
-    <row r="41" spans="1:15" ht="50" customHeight="1"/>
-    <row r="42" spans="1:15" ht="50" customHeight="1"/>
-    <row r="43" spans="1:15" ht="50" customHeight="1"/>
-    <row r="44" spans="1:15" ht="50" customHeight="1"/>
-    <row r="45" spans="1:15" ht="50" customHeight="1"/>
-    <row r="46" spans="1:15" ht="50" customHeight="1"/>
-    <row r="47" spans="1:15" ht="50" customHeight="1"/>
-    <row r="48" spans="1:15" ht="50" customHeight="1"/>
+    <row r="38" spans="1:16" ht="50" customHeight="1"/>
+    <row r="39" spans="1:16" ht="50" customHeight="1"/>
+    <row r="40" spans="1:16" ht="50" customHeight="1"/>
+    <row r="41" spans="1:16" ht="50" customHeight="1"/>
+    <row r="42" spans="1:16" ht="50" customHeight="1"/>
+    <row r="43" spans="1:16" ht="50" customHeight="1"/>
+    <row r="44" spans="1:16" ht="50" customHeight="1"/>
+    <row r="45" spans="1:16" ht="50" customHeight="1"/>
+    <row r="46" spans="1:16" ht="50" customHeight="1"/>
+    <row r="47" spans="1:16" ht="50" customHeight="1"/>
+    <row r="48" spans="1:16" ht="50" customHeight="1"/>
     <row r="49" ht="50" customHeight="1"/>
     <row r="50" ht="50" customHeight="1"/>
     <row r="51" ht="50" customHeight="1"/>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -7792,7 +7792,11 @@
       <c r="H4" s="10">
         <v>30</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>14224_1</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="s">
         <v>715</v>
       </c>

--- a/dangeon.xlsx
+++ b/dangeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aoi21\Downloads\web_try2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4D04676-E412-AC49-AA49-A4CD77DE77AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E86341-95FF-0C49-8232-C4A466815A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E2A9CB92-BD41-4511-9955-5826BD74E9FF}"/>
   </bookViews>
   <sheets>
     <sheet name="dangeon" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="737">
   <si>
     <t>奈落の重界</t>
   </si>
@@ -7792,10 +7792,8 @@
       <c r="H4" s="10">
         <v>30</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>14224_1</t>
-        </is>
+      <c r="I4" s="10" t="s">
+        <v>727</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>715</v>
